--- a/public/matriz_backlog.xlsx
+++ b/public/matriz_backlog.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joel/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miguelangelpacheco/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9FB144-B919-D643-ABE6-AB4FBC070C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299F00D9-4004-9E44-B8A7-1854A6D991D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="560" windowWidth="29920" windowHeight="16980" xr2:uid="{F5EBCA54-F250-EF45-B6B3-60EFDB3A97A7}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{F5EBCA54-F250-EF45-B6B3-60EFDB3A97A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos - Nego - Regu" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proyectos - Nego - Regu'!$A$1:$L$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proyectos - Nego - Regu'!$A$1:$L$42</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="166">
   <si>
     <t>Proyecto</t>
   </si>
@@ -125,16 +125,10 @@
     <t>Negocio</t>
   </si>
   <si>
-    <t>Piloto</t>
-  </si>
-  <si>
     <t>Segmentación B2C única para herramientas - Parte2</t>
   </si>
   <si>
     <t>Julio</t>
-  </si>
-  <si>
-    <t>15/09 - 21/09</t>
   </si>
   <si>
     <t>Miguel Pacheco</t>
@@ -175,9 +169,6 @@
   </si>
   <si>
     <t>16/09 - 23/09</t>
-  </si>
-  <si>
-    <t>25/09 - 07/10</t>
   </si>
   <si>
     <t>Roberto V / Bryan</t>
@@ -190,9 +181,6 @@
   </si>
   <si>
     <t>Subsanación de huelas Fase 3 - Regeneración de contratos</t>
-  </si>
-  <si>
-    <t>9/10 - 14/10</t>
   </si>
   <si>
     <t>Dito - Proceso de subsanación Inconsistencia de Materiales</t>
@@ -411,9 +399,6 @@
   </si>
   <si>
     <t>01/07 - 08/07</t>
-  </si>
-  <si>
-    <t>24/09 - 30/10</t>
   </si>
   <si>
     <t>Carlos</t>
@@ -751,6 +736,44 @@
       </rPr>
       <t>PROI-382</t>
     </r>
+  </si>
+  <si>
+    <t>15/09 - 23/09</t>
+  </si>
+  <si>
+    <t>Adecuación de DITO (Web y App), App Ventas Móvil y Contrato HP para la evidencia del Consentimiento</t>
+  </si>
+  <si>
+    <t>PROI-739
+PROI-938</t>
+  </si>
+  <si>
+    <t>PROI-739
+PROI-939</t>
+  </si>
+  <si>
+    <t>01/10 - 15/10</t>
+  </si>
+  <si>
+    <t>Certificado</t>
+  </si>
+  <si>
+    <t>28/09 - 29/09</t>
+  </si>
+  <si>
+    <t>25/09 - 29/09</t>
+  </si>
+  <si>
+    <t>25/09 - 05/10</t>
+  </si>
+  <si>
+    <t>5/10 - 9/10</t>
+  </si>
+  <si>
+    <t>Listo para desarrollar</t>
+  </si>
+  <si>
+    <t>16/10 - 22/10</t>
   </si>
 </sst>
 </file>
@@ -1015,7 +1038,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1169,6 +1192,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1533,7 +1569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B6F68A8-D7AA-5040-AAF5-F610612294E8}">
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="16" customWidth="1"/>
@@ -1588,7 +1624,7 @@
     </row>
     <row r="2" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B2" s="27" t="s">
         <v>12</v>
@@ -1624,7 +1660,7 @@
     </row>
     <row r="3" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="26" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>21</v>
@@ -1653,15 +1689,15 @@
         <v>25</v>
       </c>
       <c r="L3" s="31" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="18" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>13</v>
@@ -1670,36 +1706,36 @@
         <v>14</v>
       </c>
       <c r="E4" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="G4" s="15">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="I4" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="G4" s="15">
-        <v>46289</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="K4" s="14" t="s">
         <v>25</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>5</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="18" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>13</v>
@@ -1711,19 +1747,19 @@
         <v>46234</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>29</v>
+        <v>160</v>
       </c>
       <c r="G5" s="15">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K5" s="14" t="s">
         <v>25</v>
@@ -1734,10 +1770,10 @@
     </row>
     <row r="6" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>13</v>
@@ -1746,20 +1782,20 @@
         <v>14</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>29</v>
+        <v>160</v>
       </c>
       <c r="G6" s="15">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I6" s="21"/>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K6" s="14" t="s">
         <v>25</v>
@@ -1770,10 +1806,10 @@
     </row>
     <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>13</v>
@@ -1785,7 +1821,7 @@
         <v>46281</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G7" s="37">
         <v>46289</v>
@@ -1794,24 +1830,24 @@
         <v>17</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K7" s="14" t="s">
         <v>25</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="18" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>13</v>
@@ -1820,10 +1856,10 @@
         <v>14</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>43</v>
+        <v>162</v>
       </c>
       <c r="G8" s="15">
         <v>46303</v>
@@ -1832,10 +1868,10 @@
         <v>17</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K8" s="14" t="s">
         <v>19</v>
@@ -1846,10 +1882,10 @@
     </row>
     <row r="9" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="18" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>13</v>
@@ -1861,17 +1897,17 @@
         <v>46055</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="G9" s="15">
         <v>46310</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I9" s="21"/>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K9" s="14" t="s">
         <v>19</v>
@@ -1882,10 +1918,10 @@
     </row>
     <row r="10" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="18" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>13</v>
@@ -1897,17 +1933,17 @@
         <v>46209</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="G10" s="15">
         <v>46310</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I10" s="21"/>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K10" s="14" t="s">
         <v>19</v>
@@ -1918,10 +1954,10 @@
     </row>
     <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="18" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>22</v>
@@ -1930,10 +1966,10 @@
         <v>14</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G11" s="9">
         <v>46310</v>
@@ -1946,7 +1982,7 @@
         <v>24</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>4</v>
@@ -1954,10 +1990,10 @@
     </row>
     <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="18" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>22</v>
@@ -1966,10 +2002,10 @@
         <v>14</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G12" s="9">
         <v>46310</v>
@@ -1982,7 +2018,7 @@
         <v>24</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>4</v>
@@ -1990,10 +2026,10 @@
     </row>
     <row r="13" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>22</v>
@@ -2002,20 +2038,20 @@
         <v>14</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G13" s="15">
         <v>46310</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I13" s="21"/>
       <c r="J13" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>25</v>
@@ -2026,10 +2062,10 @@
     </row>
     <row r="14" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>22</v>
@@ -2038,10 +2074,10 @@
         <v>14</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G14" s="15">
         <v>46331</v>
@@ -2050,10 +2086,10 @@
         <v>17</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K14" s="14" t="s">
         <v>25</v>
@@ -2064,10 +2100,10 @@
     </row>
     <row r="15" spans="1:12" ht="85" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>13</v>
@@ -2076,10 +2112,10 @@
         <v>14</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G15" s="15">
         <v>46331</v>
@@ -2088,10 +2124,10 @@
         <v>17</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="K15" s="14" t="s">
         <v>19</v>
@@ -2102,10 +2138,10 @@
     </row>
     <row r="16" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" s="18" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>13</v>
@@ -2114,22 +2150,22 @@
         <v>14</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F16" s="47" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G16" s="47">
         <v>46347</v>
       </c>
       <c r="H16" s="48" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J16" s="46" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="K16" s="49" t="s">
         <v>25</v>
@@ -2140,10 +2176,10 @@
     </row>
     <row r="17" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="19" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>13</v>
@@ -2152,16 +2188,16 @@
         <v>14</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G17" s="15">
         <v>46352</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="2"/>
@@ -2174,10 +2210,10 @@
     </row>
     <row r="18" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>13</v>
@@ -2186,34 +2222,34 @@
         <v>14</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H18" s="51" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I18" s="43"/>
       <c r="J18" s="39" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K18" s="40" t="s">
         <v>19</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>13</v>
@@ -2222,20 +2258,20 @@
         <v>46283</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H19" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I19" s="21"/>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K19" s="14" t="s">
         <v>25</v>
@@ -2246,10 +2282,10 @@
     </row>
     <row r="20" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>13</v>
@@ -2267,7 +2303,7 @@
         <v>14</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I20" s="21"/>
       <c r="J20" s="2" t="s">
@@ -2277,33 +2313,33 @@
         <v>19</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" s="18" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I21" s="21"/>
       <c r="J21" s="2" t="s">
@@ -2318,64 +2354,64 @@
     </row>
     <row r="22" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A22" s="33" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H22" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I22" s="21"/>
       <c r="J22" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K22" s="14" t="s">
         <v>25</v>
       </c>
       <c r="L22" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="34" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I23" s="21"/>
       <c r="J23" s="14" t="s">
@@ -2385,30 +2421,30 @@
         <v>25</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="34" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H24" s="21" t="s">
         <v>17</v>
@@ -2421,67 +2457,67 @@
         <v>25</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A25" s="52" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I25" s="21"/>
       <c r="J25" s="14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K25" s="14" t="s">
         <v>25</v>
       </c>
       <c r="L25" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A26" s="52" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I26" s="21"/>
       <c r="J26" s="14" t="s">
@@ -2491,33 +2527,33 @@
         <v>19</v>
       </c>
       <c r="L26" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="34" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G27" s="37">
         <v>46366</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I27" s="21"/>
       <c r="J27" s="14" t="s">
@@ -2527,30 +2563,30 @@
         <v>25</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="34" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H28" s="34" t="s">
         <v>17</v>
@@ -2563,33 +2599,33 @@
         <v>25</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="34" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H29" s="21" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I29" s="12"/>
       <c r="J29" s="14" t="s">
@@ -2599,30 +2635,30 @@
         <v>25</v>
       </c>
       <c r="L29" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="34" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H30" s="21" t="s">
         <v>17</v>
@@ -2635,15 +2671,15 @@
         <v>25</v>
       </c>
       <c r="L30" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A31" s="23" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>13</v>
@@ -2661,16 +2697,16 @@
         <v>46296</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I31" s="22" t="s">
         <v>14</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>4</v>
@@ -2678,13 +2714,13 @@
     </row>
     <row r="32" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>14</v>
@@ -2699,16 +2735,16 @@
         <v>46236</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I32" s="22" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>5</v>
@@ -2716,48 +2752,48 @@
     </row>
     <row r="33" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A33" s="23" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G33" s="9">
         <v>46353</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I33" s="22" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="23" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>13</v>
@@ -2766,25 +2802,25 @@
         <v>14</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="G34" s="9">
-        <v>46296</v>
+        <v>46303</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L34" s="1" t="s">
         <v>5</v>
@@ -2792,10 +2828,10 @@
     </row>
     <row r="35" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="23" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>22</v>
@@ -2820,138 +2856,138 @@
         <v>24</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="23" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I36" s="22"/>
       <c r="J36" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="23" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I37" s="22"/>
       <c r="J37" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A38" s="23" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H38" s="21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I38" s="21"/>
       <c r="J38" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L38" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="34" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D39" s="14" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="42" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G39" s="37">
         <v>46303</v>
@@ -2961,10 +2997,10 @@
       </c>
       <c r="I39" s="22"/>
       <c r="J39" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>4</v>
@@ -2972,42 +3008,97 @@
     </row>
     <row r="40" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="34" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I40" s="22"/>
       <c r="J40" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A41" s="53" t="s">
+        <v>156</v>
+      </c>
+      <c r="B41" t="s">
+        <v>155</v>
+      </c>
+      <c r="C41" s="54" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s">
+        <v>158</v>
+      </c>
+      <c r="F41" s="57" t="s">
+        <v>165</v>
+      </c>
+      <c r="G41" s="56">
+        <v>46324</v>
+      </c>
+      <c r="H41" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="J41" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A42" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="B42" t="s">
+        <v>155</v>
+      </c>
+      <c r="C42" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" t="s">
+        <v>158</v>
+      </c>
+      <c r="G42" s="56">
+        <v>46331</v>
+      </c>
+      <c r="H42" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="J42" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L26" xr:uid="{8B6F68A8-D7AA-5040-AAF5-F610612294E8}">
+  <autoFilter ref="A1:L42" xr:uid="{8B6F68A8-D7AA-5040-AAF5-F610612294E8}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L26">
       <sortCondition ref="G1:G26"/>
     </sortState>

--- a/public/matriz_backlog.xlsx
+++ b/public/matriz_backlog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miguelangelpacheco/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miguelangelpacheco/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299F00D9-4004-9E44-B8A7-1854A6D991D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CFFD06-97AC-BB4C-B757-2A4CF6A2492B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{F5EBCA54-F250-EF45-B6B3-60EFDB3A97A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="166">
   <si>
     <t>Proyecto</t>
   </si>
@@ -1038,7 +1038,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1204,7 +1204,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3067,6 +3070,9 @@
       <c r="J41" s="54" t="s">
         <v>32</v>
       </c>
+      <c r="K41" s="58" t="s">
+        <v>19</v>
+      </c>
       <c r="L41" s="16" t="s">
         <v>164</v>
       </c>
@@ -3092,6 +3098,9 @@
       </c>
       <c r="J42" s="54" t="s">
         <v>24</v>
+      </c>
+      <c r="K42" s="58" t="s">
+        <v>19</v>
       </c>
       <c r="L42" s="16" t="s">
         <v>164</v>

--- a/public/matriz_backlog.xlsx
+++ b/public/matriz_backlog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miguelangelpacheco/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CFFD06-97AC-BB4C-B757-2A4CF6A2492B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D877515B-083E-4932-AB3F-055616362A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{F5EBCA54-F250-EF45-B6B3-60EFDB3A97A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="165">
   <si>
     <t>Proyecto</t>
   </si>
@@ -78,6 +78,21 @@
   </si>
   <si>
     <t>Estado</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PROI-295
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Cuerpo)"/>
+      </rPr>
+      <t>PROI-488</t>
+    </r>
   </si>
   <si>
     <t>Flujo de venta para extranjeros desde Dito WEB - Canales presenciales</t>
@@ -110,6 +125,21 @@
     <t>Produccion</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">PROI-43
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Cuerpo)"/>
+      </rPr>
+      <t>PROI-382</t>
+    </r>
+  </si>
+  <si>
     <t>Venta de alta pura MT en APP DITO</t>
   </si>
   <si>
@@ -125,10 +155,28 @@
     <t>Negocio</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">PROI-511
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Cuerpo)"/>
+      </rPr>
+      <t>PROI-712</t>
+    </r>
+  </si>
+  <si>
     <t>Segmentación B2C única para herramientas - Parte2</t>
   </si>
   <si>
     <t>Julio</t>
+  </si>
+  <si>
+    <t>15/09 - 23/09</t>
   </si>
   <si>
     <t>Miguel Pacheco</t>
@@ -138,15 +186,54 @@
 ms-dito-customer</t>
   </si>
   <si>
+    <t>Certificado</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PROI-629
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Cuerpo)"/>
+      </rPr>
+      <t>PROI-723</t>
+    </r>
+  </si>
+  <si>
     <t>Venta de eSIM Retail Dito</t>
   </si>
   <si>
+    <t>28/09 - 29/09</t>
+  </si>
+  <si>
+    <t>Joel T.</t>
+  </si>
+  <si>
     <t>Roberto V.</t>
   </si>
   <si>
     <t>Front</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">PROI-653
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Cuerpo)"/>
+      </rPr>
+      <t>PROI-670</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Migración del proceso de devoluciones de venta móvil </t>
   </si>
   <si>
@@ -162,13 +249,29 @@
     <t>17/09 - 21/09</t>
   </si>
   <si>
-    <t>Definicion</t>
+    <r>
+      <t xml:space="preserve">
+PROI-119
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Cuerpo)"/>
+      </rPr>
+      <t>PROI-703</t>
+    </r>
   </si>
   <si>
     <t>[CR4151 D63] Transformación del Modelo de Apellidos del Contacto</t>
   </si>
   <si>
     <t>16/09 - 23/09</t>
+  </si>
+  <si>
+    <t>25/09 - 05/10</t>
   </si>
   <si>
     <t>Roberto V / Bryan</t>
@@ -180,9 +283,42 @@
 ms-dito-customer</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">PROI-49
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Cuerpo)"/>
+      </rPr>
+      <t>PROI-392</t>
+    </r>
+  </si>
+  <si>
     <t>Subsanación de huelas Fase 3 - Regeneración de contratos</t>
   </si>
   <si>
+    <t>5/10 - 9/10</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PROI-119
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Cuerpo)"/>
+      </rPr>
+      <t>PROI-424</t>
+    </r>
+  </si>
+  <si>
     <t>Dito - Proceso de subsanación Inconsistencia de Materiales</t>
   </si>
   <si>
@@ -205,6 +341,36 @@
   </si>
   <si>
     <t xml:space="preserve">Registrar dirección de instalación desde la ubicación </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PROI-511
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Cuerpo)"/>
+      </rPr>
+      <t>PROI-713</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PROI-406
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Cuerpo)"/>
+      </rPr>
+      <t>PROI-443</t>
+    </r>
   </si>
   <si>
     <t>Biometría Facial Implementacion Dito</t>
@@ -221,6 +387,21 @@
   <si>
     <t>Apk
 ms-dito-customerValidation</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">PROI-368
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Cuerpo)"/>
+      </rPr>
+      <t>PROI-746</t>
+    </r>
   </si>
   <si>
     <t>Carga de Documento de Identidad y Validacion de Token</t>
@@ -242,6 +423,21 @@
 ms-dito-KeyVault</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">PROI-246
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Cuerpo)"/>
+      </rPr>
+      <t>PROI-518</t>
+    </r>
+  </si>
+  <si>
     <t>Venta de accesorios DITO</t>
   </si>
   <si>
@@ -254,202 +450,6 @@
     <t>Front
 ms-dito-saleslead
 ms-dito-sales</t>
-  </si>
-  <si>
-    <t>Subsanación de huellas para B2B</t>
-  </si>
-  <si>
-    <t>16/11 - 20/11</t>
-  </si>
-  <si>
-    <t>23/11 - 27/11</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>Planificado</t>
-  </si>
-  <si>
-    <t>PROI-628</t>
-  </si>
-  <si>
-    <t>Transformacion de modelo venta Fija y MT</t>
-  </si>
-  <si>
-    <t>PROI-517</t>
-  </si>
-  <si>
-    <t>Adecuaciones en la validación biométrica RENIEC/MIGRACIONES y venta a Clientes Extranjeros en otros canales</t>
-  </si>
-  <si>
-    <t>Cancelado</t>
-  </si>
-  <si>
-    <t>Digitalización de eSIM - Fase 1</t>
-  </si>
-  <si>
-    <t>09/10 - 16/10</t>
-  </si>
-  <si>
-    <t>01/11 - 20/11</t>
-  </si>
-  <si>
-    <t>14/12 - 18/12</t>
-  </si>
-  <si>
-    <t>REQI-874</t>
-  </si>
-  <si>
-    <t>Activación de Contingencia para Continuidad de Ventas sin RENIEC Canal Presencial</t>
-  </si>
-  <si>
-    <t>9/10 - 16/10</t>
-  </si>
-  <si>
-    <t>Front
-Backend</t>
-  </si>
-  <si>
-    <t>PROI-861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biometria Vendedor Nacional con Reniec para Alta, Porta, CATI </t>
-  </si>
-  <si>
-    <t>9/10 - 15/10</t>
-  </si>
-  <si>
-    <t>Joel T.</t>
-  </si>
-  <si>
-    <t>PROI-722</t>
-  </si>
-  <si>
-    <t>TV App</t>
-  </si>
-  <si>
-    <t>Adecuaciones en el consentimiento y contratos del Cliente</t>
-  </si>
-  <si>
-    <t>5/10 - 09/10</t>
-  </si>
-  <si>
-    <t>Actualización de Condiciones de Uso (CDU)- Adecuaciones en herramientas - Parte 2</t>
-  </si>
-  <si>
-    <t>28/09 - 09/10</t>
-  </si>
-  <si>
-    <t>PROI-784</t>
-  </si>
-  <si>
-    <t>Continuidad de ventas sin RENIEC</t>
-  </si>
-  <si>
-    <t>Web/App</t>
-  </si>
-  <si>
-    <t>REQI-572</t>
-  </si>
-  <si>
-    <t>Visualización en Dito opción repetidor Comodato y Alquiler</t>
-  </si>
-  <si>
-    <t>PROI-858</t>
-  </si>
-  <si>
-    <t>Adecuaciones en la validación biométrica RENIEC/MIGRACIONES y venta a Clientes Extranjeros</t>
-  </si>
-  <si>
-    <t>REQI-846</t>
-  </si>
-  <si>
-    <t>Tren Apollo | Atención de Mejoras // Gaps // Incidencias // Configuraciones de aplicaciones Apollo - Setiembre</t>
-  </si>
-  <si>
-    <t>REQI-858</t>
-  </si>
-  <si>
-    <t>Tren Apollo | Upgrade de Framework a Genesis 3.3 - Setiembre</t>
-  </si>
-  <si>
-    <t>Backend</t>
-  </si>
-  <si>
-    <t>New</t>
-  </si>
-  <si>
-    <t>REQI-152</t>
-  </si>
-  <si>
-    <t>Implementación de Web Admin para Dito</t>
-  </si>
-  <si>
-    <t>Carlos / New</t>
-  </si>
-  <si>
-    <t>Listo para refinar</t>
-  </si>
-  <si>
-    <t>REQI-149</t>
-  </si>
-  <si>
-    <t>Refactorización del formulario de direcciones para ventas moviles</t>
-  </si>
-  <si>
-    <t>01/07 - 08/07</t>
-  </si>
-  <si>
-    <t>Carlos</t>
-  </si>
-  <si>
-    <t>REQI-322</t>
-  </si>
-  <si>
-    <t>Nueva Pantalla de Ofertas App DITO</t>
-  </si>
-  <si>
-    <t>REQI-809</t>
-  </si>
-  <si>
-    <t>Monitoreo Diario-Flujo de subsanación cliente extranjero B2C</t>
-  </si>
-  <si>
-    <t>REQI-816</t>
-  </si>
-  <si>
-    <t>Control de Pedidos Duplicados en Canal CC</t>
-  </si>
-  <si>
-    <t>02/11 - 06/11</t>
-  </si>
-  <si>
-    <t>Unificación de Activadores – Integración de plataformas Móvil, Fija (FTTH) y OTT en una única solución centralizada</t>
-  </si>
-  <si>
-    <t>REQI -876</t>
-  </si>
-  <si>
-    <t>Migración function runtime - java 21 - DITO</t>
-  </si>
-  <si>
-    <t>07/09 - 25/09</t>
-  </si>
-  <si>
-    <t>28/09 - 02/10</t>
-  </si>
-  <si>
-    <t>Functions</t>
-  </si>
-  <si>
-    <t>REQI-823</t>
-  </si>
-  <si>
-    <t>Optimizar el campo del Housing ComplexX2 para direcciones extendidas</t>
-  </si>
-  <si>
-    <t>15/10 - 20/10</t>
   </si>
   <si>
     <r>
@@ -467,9 +467,6 @@
     </r>
   </si>
   <si>
-    <t>Miguel / Juan Pablo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nuevo flujo de ventas para Cambio de Equipo en los canales de Retail y Islas </t>
   </si>
   <si>
@@ -477,157 +474,6 @@
   </si>
   <si>
     <t>16/11 - 25/11</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">PROI-511
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow (Cuerpo)"/>
-      </rPr>
-      <t>PROI-712</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">PROI-629
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow (Cuerpo)"/>
-      </rPr>
-      <t>PROI-723</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">PROI-653
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow (Cuerpo)"/>
-      </rPr>
-      <t>PROI-670</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">
-PROI-119
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow (Cuerpo)"/>
-      </rPr>
-      <t>PROI-703</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">PROI-49
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow (Cuerpo)"/>
-      </rPr>
-      <t>PROI-392</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">PROI-119
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow (Cuerpo)"/>
-      </rPr>
-      <t>PROI-424</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">PROI-511
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow (Cuerpo)"/>
-      </rPr>
-      <t>PROI-713</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">PROI-406
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow (Cuerpo)"/>
-      </rPr>
-      <t>PROI-443</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">PROI-368
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow (Cuerpo)"/>
-      </rPr>
-      <t>PROI-746</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">PROI-246
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow (Cuerpo)"/>
-      </rPr>
-      <t>PROI-518</t>
-    </r>
   </si>
   <si>
     <r>
@@ -645,6 +491,36 @@
     </r>
   </si>
   <si>
+    <t>Subsanación de huellas para B2B</t>
+  </si>
+  <si>
+    <t>16/11 - 20/11</t>
+  </si>
+  <si>
+    <t>23/11 - 27/11</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Planificado</t>
+  </si>
+  <si>
+    <t>PROI-628</t>
+  </si>
+  <si>
+    <t>Transformacion de modelo venta Fija y MT</t>
+  </si>
+  <si>
+    <t>PROI-517</t>
+  </si>
+  <si>
+    <t>Adecuaciones en la validación biométrica RENIEC/MIGRACIONES y venta a Clientes Extranjeros en otros canales</t>
+  </si>
+  <si>
+    <t>Cancelado</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">PROI-122
 </t>
@@ -660,6 +536,49 @@
     </r>
   </si>
   <si>
+    <t>Digitalización de eSIM - Fase 1</t>
+  </si>
+  <si>
+    <t>09/10 - 16/10</t>
+  </si>
+  <si>
+    <t>01/11 - 20/11</t>
+  </si>
+  <si>
+    <t>14/12 - 18/12</t>
+  </si>
+  <si>
+    <t>REQI-874</t>
+  </si>
+  <si>
+    <t>Activación de Contingencia para Continuidad de Ventas sin RENIEC Canal Presencial</t>
+  </si>
+  <si>
+    <t>9/10 - 16/10</t>
+  </si>
+  <si>
+    <t>Front
+Backend</t>
+  </si>
+  <si>
+    <t>Definicion</t>
+  </si>
+  <si>
+    <t>PROI-861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biometria Vendedor Nacional con Reniec para Alta, Porta, CATI </t>
+  </si>
+  <si>
+    <t>9/10 - 15/10</t>
+  </si>
+  <si>
+    <t>PROI-722</t>
+  </si>
+  <si>
+    <t>TV App</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">PROI-739
 </t>
@@ -675,6 +594,12 @@
     </r>
   </si>
   <si>
+    <t>Adecuaciones en el consentimiento y contratos del Cliente</t>
+  </si>
+  <si>
+    <t>5/10 - 09/10</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">PROI-255
 </t>
@@ -690,7 +615,103 @@
     </r>
   </si>
   <si>
+    <t>Actualización de Condiciones de Uso (CDU)- Adecuaciones en herramientas - Parte 2</t>
+  </si>
+  <si>
     <t>PROI-852</t>
+  </si>
+  <si>
+    <t>28/09 - 09/10</t>
+  </si>
+  <si>
+    <t>Miguel / Juan Pablo</t>
+  </si>
+  <si>
+    <t>PROI-784</t>
+  </si>
+  <si>
+    <t>Continuidad de ventas sin RENIEC</t>
+  </si>
+  <si>
+    <t>Web/App</t>
+  </si>
+  <si>
+    <t>REQI-572</t>
+  </si>
+  <si>
+    <t>Visualización en Dito opción repetidor Comodato y Alquiler</t>
+  </si>
+  <si>
+    <t>PROI-858</t>
+  </si>
+  <si>
+    <t>Adecuaciones en la validación biométrica RENIEC/MIGRACIONES y venta a Clientes Extranjeros</t>
+  </si>
+  <si>
+    <t>REQI-846</t>
+  </si>
+  <si>
+    <t>Tren Apollo | Atención de Mejoras // Gaps // Incidencias // Configuraciones de aplicaciones Apollo - Setiembre</t>
+  </si>
+  <si>
+    <t>REQI-858</t>
+  </si>
+  <si>
+    <t>Tren Apollo | Upgrade de Framework a Genesis 3.3 - Setiembre</t>
+  </si>
+  <si>
+    <t>Backend</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>REQI-152</t>
+  </si>
+  <si>
+    <t>Implementación de Web Admin para Dito</t>
+  </si>
+  <si>
+    <t>Carlos / New</t>
+  </si>
+  <si>
+    <t>Listo para refinar</t>
+  </si>
+  <si>
+    <t>REQI-149</t>
+  </si>
+  <si>
+    <t>Refactorización del formulario de direcciones para ventas moviles</t>
+  </si>
+  <si>
+    <t>01/07 - 08/07</t>
+  </si>
+  <si>
+    <t>25/09 - 29/09</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>REQI-322</t>
+  </si>
+  <si>
+    <t>Nueva Pantalla de Ofertas App DITO</t>
+  </si>
+  <si>
+    <t>REQI-809</t>
+  </si>
+  <si>
+    <t>Monitoreo Diario-Flujo de subsanación cliente extranjero B2C</t>
+  </si>
+  <si>
+    <t>REQI-816</t>
+  </si>
+  <si>
+    <t>Control de Pedidos Duplicados en Canal CC</t>
+  </si>
+  <si>
+    <t>02/11 - 06/11</t>
   </si>
   <si>
     <r>
@@ -708,79 +729,55 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">PROI-295
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow (Cuerpo)"/>
-      </rPr>
-      <t>PROI-488</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">PROI-43
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow (Cuerpo)"/>
-      </rPr>
-      <t>PROI-382</t>
-    </r>
-  </si>
-  <si>
-    <t>15/09 - 23/09</t>
+    <t>Unificación de Activadores – Integración de plataformas Móvil, Fija (FTTH) y OTT en una única solución centralizada</t>
+  </si>
+  <si>
+    <t>REQI -876</t>
+  </si>
+  <si>
+    <t>Migración function runtime - java 21 - DITO</t>
+  </si>
+  <si>
+    <t>07/09 - 25/09</t>
+  </si>
+  <si>
+    <t>28/09 - 02/10</t>
+  </si>
+  <si>
+    <t>Functions</t>
+  </si>
+  <si>
+    <t>REQI-823</t>
+  </si>
+  <si>
+    <t>Optimizar el campo del Housing ComplexX2 para direcciones extendidas</t>
+  </si>
+  <si>
+    <t>15/10 - 20/10</t>
+  </si>
+  <si>
+    <t>PROI-739
+PROI-937</t>
   </si>
   <si>
     <t>Adecuación de DITO (Web y App), App Ventas Móvil y Contrato HP para la evidencia del Consentimiento</t>
+  </si>
+  <si>
+    <t>01/10 - 15/10</t>
+  </si>
+  <si>
+    <t>16/10 - 22/10</t>
   </si>
   <si>
     <t>PROI-739
 PROI-938</t>
-  </si>
-  <si>
-    <t>PROI-739
-PROI-939</t>
-  </si>
-  <si>
-    <t>01/10 - 15/10</t>
-  </si>
-  <si>
-    <t>Certificado</t>
-  </si>
-  <si>
-    <t>28/09 - 29/09</t>
-  </si>
-  <si>
-    <t>25/09 - 29/09</t>
-  </si>
-  <si>
-    <t>25/09 - 05/10</t>
-  </si>
-  <si>
-    <t>5/10 - 9/10</t>
-  </si>
-  <si>
-    <t>Listo para desarrollar</t>
-  </si>
-  <si>
-    <t>16/10 - 22/10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1038,7 +1035,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1192,22 +1189,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1573,21 +1554,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B6F68A8-D7AA-5040-AAF5-F610612294E8}">
   <dimension ref="A1:L42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="10.375" style="16" customWidth="1"/>
     <col min="2" max="2" width="79" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.83203125" customWidth="1"/>
+    <col min="4" max="4" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.1640625" customWidth="1"/>
-    <col min="10" max="10" width="30.6640625" customWidth="1"/>
+    <col min="8" max="8" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.125" customWidth="1"/>
+    <col min="10" max="10" width="30.625" customWidth="1"/>
     <col min="11" max="11" width="10.5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.5" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1625,1485 +1606,1490 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="68.099999999999994">
       <c r="A2" s="26" t="s">
-        <v>152</v>
+        <v>12</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="29">
         <v>46275</v>
       </c>
       <c r="H2" s="30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" s="30"/>
       <c r="J2" s="28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" s="31" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="32.1">
       <c r="A3" s="26" t="s">
-        <v>153</v>
+        <v>22</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" s="28"/>
       <c r="E3" s="29">
         <v>46079</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3" s="32">
         <v>46286</v>
       </c>
       <c r="H3" s="30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" s="30"/>
       <c r="J3" s="28" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K3" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L3" s="31" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="30.75">
       <c r="A4" s="18" t="s">
-        <v>136</v>
+        <v>28</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="15">
+        <v>46300</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="30.75">
+      <c r="A5" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="G4" s="15">
-        <v>46296</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="15">
         <v>46234</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>160</v>
+        <v>37</v>
       </c>
       <c r="G5" s="15">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="30.75">
       <c r="A6" s="18" t="s">
-        <v>138</v>
+        <v>41</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>160</v>
+        <v>37</v>
       </c>
       <c r="G6" s="15">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I6" s="21"/>
       <c r="J6" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="17.100000000000001">
       <c r="A7" s="18" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="15">
         <v>46281</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="G7" s="37">
         <v>46289</v>
       </c>
       <c r="H7" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L7" s="14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="68.099999999999994">
       <c r="A8" s="18" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>162</v>
+        <v>50</v>
       </c>
       <c r="G8" s="15">
         <v>46303</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L8" s="14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="32.1">
       <c r="A9" s="18" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" s="15">
         <v>46055</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>163</v>
+        <v>55</v>
       </c>
       <c r="G9" s="15">
         <v>46310</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I9" s="21"/>
       <c r="J9" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L9" s="14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="32.1">
       <c r="A10" s="18" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" s="15">
         <v>46209</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>163</v>
+        <v>55</v>
       </c>
       <c r="G10" s="15">
         <v>46310</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I10" s="21"/>
       <c r="J10" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L10" s="14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="17.100000000000001">
       <c r="A11" s="18" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G11" s="9">
         <v>46310</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I11" s="22"/>
       <c r="J11" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="17.100000000000001">
       <c r="A12" s="18" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G12" s="9">
         <v>46310</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I12" s="22"/>
       <c r="J12" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="33.950000000000003">
       <c r="A13" s="18" t="s">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G13" s="15">
         <v>46310</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I13" s="21"/>
       <c r="J13" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L13" s="14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="33.950000000000003">
       <c r="A14" s="18" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="G14" s="15">
         <v>46331</v>
       </c>
       <c r="H14" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L14" s="14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="84.95">
       <c r="A15" s="18" t="s">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="G15" s="15">
         <v>46331</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L15" s="14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="51">
       <c r="A16" s="18" t="s">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="F16" s="47" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="G16" s="47">
         <v>46347</v>
       </c>
       <c r="H16" s="48" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="J16" s="46" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="K16" s="49" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L16" s="49" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="47" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="47.1" customHeight="1">
       <c r="A17" s="19" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>134</v>
+        <v>85</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="G17" s="15">
         <v>46352</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="2"/>
       <c r="K17" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L17" s="14" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="32.1">
       <c r="A18" s="18" t="s">
-        <v>146</v>
+        <v>87</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" s="50" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="H18" s="51" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="I18" s="43"/>
       <c r="J18" s="39" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K18" s="40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="17.100000000000001">
       <c r="A19" s="18" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" s="11">
         <v>46283</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I19" s="21"/>
       <c r="J19" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L19" s="14" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="33.950000000000003">
       <c r="A20" s="18" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I20" s="21"/>
       <c r="J20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="32.1">
+      <c r="A21" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K20" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="L20" s="14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A21" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="I21" s="21"/>
       <c r="J21" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L21" s="14" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="33.950000000000003">
       <c r="A22" s="33" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I22" s="21"/>
       <c r="J22" s="2" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L22" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="17.100000000000001">
+      <c r="A23" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H23" s="21" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="B23" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="H23" s="21" t="s">
-        <v>87</v>
       </c>
       <c r="I23" s="21"/>
       <c r="J23" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="17.100000000000001">
       <c r="A24" s="34" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="H24" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I24" s="21"/>
       <c r="J24" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="32.1">
+      <c r="A25" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K24" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="L24" s="14" t="s">
+      <c r="D25" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25" s="21" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A25" s="52" t="s">
-        <v>148</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="H25" s="21" t="s">
-        <v>87</v>
       </c>
       <c r="I25" s="21"/>
       <c r="J25" s="14" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K25" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L25" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="32.1">
       <c r="A26" s="52" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="I26" s="21"/>
       <c r="J26" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="17.100000000000001">
+      <c r="A27" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K26" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="L26" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A27" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D27" s="14" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G27" s="37">
         <v>46366</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="I27" s="21"/>
       <c r="J27" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="17.100000000000001">
       <c r="A28" s="34" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="H28" s="34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I28" s="34"/>
       <c r="J28" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="17.100000000000001">
+      <c r="A29" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K28" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="L28" s="14" t="s">
+      <c r="D29" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H29" s="21" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A29" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="H29" s="21" t="s">
-        <v>87</v>
       </c>
       <c r="I29" s="12"/>
       <c r="J29" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="L29" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="17.100000000000001">
+      <c r="A30" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K29" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="L29" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A30" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D30" s="14" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="H30" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I30" s="12"/>
       <c r="J30" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="L30" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="33.950000000000003">
+      <c r="A31" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K30" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="L30" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A31" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D31" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G31" s="9">
         <v>46296</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="I31" s="22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="17.100000000000001">
       <c r="A32" s="23" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G32" s="9">
         <v>46236</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="I32" s="22" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="33.950000000000003">
       <c r="A33" s="23" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G33" s="9">
         <v>46353</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I33" s="22" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="17.100000000000001">
       <c r="A34" s="23" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="G34" s="9">
         <v>46303</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L34" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="17.100000000000001">
       <c r="A35" s="23" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I35" s="22"/>
       <c r="J35" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="17.100000000000001">
       <c r="A36" s="23" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I36" s="22"/>
       <c r="J36" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="17.100000000000001">
       <c r="A37" s="23" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="I37" s="22"/>
       <c r="J37" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="33.950000000000003">
       <c r="A38" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="C38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="H38" s="21" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I38" s="21"/>
       <c r="J38" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L38" s="14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="17.100000000000001">
       <c r="A39" s="34" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E39" s="42" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="G39" s="37">
         <v>46303</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I39" s="22"/>
       <c r="J39" s="1" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="17.100000000000001">
       <c r="A40" s="34" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="I40" s="22"/>
       <c r="J40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="30.75">
+      <c r="A41" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G41" s="37">
+        <v>46324</v>
+      </c>
+      <c r="H41" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A41" s="53" t="s">
-        <v>156</v>
-      </c>
-      <c r="B41" t="s">
-        <v>155</v>
-      </c>
-      <c r="C41" s="54" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" t="s">
-        <v>158</v>
-      </c>
-      <c r="F41" s="57" t="s">
-        <v>165</v>
-      </c>
-      <c r="G41" s="56">
-        <v>46324</v>
-      </c>
-      <c r="H41" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="J41" s="54" t="s">
-        <v>32</v>
-      </c>
-      <c r="K41" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="L41" s="16" t="s">
+      <c r="I41" s="21"/>
+      <c r="J41" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="L41" s="14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="30.75">
+      <c r="A42" s="23" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A42" s="53" t="s">
-        <v>157</v>
-      </c>
-      <c r="B42" t="s">
-        <v>155</v>
-      </c>
-      <c r="C42" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="E42" t="s">
-        <v>158</v>
-      </c>
-      <c r="G42" s="56">
+      <c r="B42" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="37">
         <v>46331</v>
       </c>
-      <c r="H42" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="J42" s="54" t="s">
-        <v>24</v>
-      </c>
-      <c r="K42" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="L42" s="16" t="s">
-        <v>164</v>
+      <c r="H42" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="I42" s="21"/>
+      <c r="J42" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="L42" s="14" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/public/matriz_backlog.xlsx
+++ b/public/matriz_backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miguelangelpacheco/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA97A4AC-067A-4FE6-9FFE-3F13D10CE945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{736AA771-0FAE-405A-8B6B-4A41CED45CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{F5EBCA54-F250-EF45-B6B3-60EFDB3A97A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="190">
   <si>
     <t>Proyecto</t>
   </si>
@@ -1741,7 +1741,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B6F68A8-D7AA-5040-AAF5-F610612294E8}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P45"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
@@ -1805,7 +1804,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="16.5" hidden="1">
+    <row r="2" spans="1:15" ht="16.5">
       <c r="A2" s="20" t="s">
         <v>15</v>
       </c>
@@ -1846,7 +1845,7 @@
       </c>
       <c r="O2" s="28"/>
     </row>
-    <row r="3" spans="1:15" ht="61.5" hidden="1">
+    <row r="3" spans="1:15" ht="61.5">
       <c r="A3" s="23" t="s">
         <v>22</v>
       </c>
@@ -1885,7 +1884,7 @@
       </c>
       <c r="O3" s="28"/>
     </row>
-    <row r="4" spans="1:15" ht="30.75" hidden="1">
+    <row r="4" spans="1:15" ht="30.75">
       <c r="A4" s="23" t="s">
         <v>31</v>
       </c>
@@ -1922,7 +1921,7 @@
       </c>
       <c r="O4" s="28"/>
     </row>
-    <row r="5" spans="1:15" ht="16.5" hidden="1">
+    <row r="5" spans="1:15" ht="16.5">
       <c r="A5" s="31" t="s">
         <v>37</v>
       </c>
@@ -1961,7 +1960,7 @@
       </c>
       <c r="O5" s="28"/>
     </row>
-    <row r="6" spans="1:15" ht="32.25" hidden="1">
+    <row r="6" spans="1:15" ht="32.25">
       <c r="A6" s="20" t="s">
         <v>42</v>
       </c>
@@ -2045,7 +2044,7 @@
       </c>
       <c r="O7" s="13"/>
     </row>
-    <row r="8" spans="1:15" ht="30.75" hidden="1">
+    <row r="8" spans="1:15" ht="30.75">
       <c r="A8" s="16" t="s">
         <v>51</v>
       </c>
@@ -2090,7 +2089,7 @@
       </c>
       <c r="O8" s="13"/>
     </row>
-    <row r="9" spans="1:15" ht="30.75" hidden="1">
+    <row r="9" spans="1:15" ht="30.75">
       <c r="A9" s="16" t="s">
         <v>56</v>
       </c>
@@ -2133,7 +2132,7 @@
       </c>
       <c r="O9" s="43"/>
     </row>
-    <row r="10" spans="1:15" ht="61.5" hidden="1">
+    <row r="10" spans="1:15" ht="61.5">
       <c r="A10" s="16" t="s">
         <v>59</v>
       </c>
@@ -2174,7 +2173,7 @@
       </c>
       <c r="O10" s="43"/>
     </row>
-    <row r="11" spans="1:15" ht="16.5" hidden="1">
+    <row r="11" spans="1:15" ht="16.5">
       <c r="A11" s="16" t="s">
         <v>65</v>
       </c>
@@ -2213,7 +2212,7 @@
       </c>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:15" ht="16.5" hidden="1">
+    <row r="12" spans="1:15" ht="16.5">
       <c r="A12" s="16" t="s">
         <v>69</v>
       </c>
@@ -2252,7 +2251,7 @@
       </c>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="1:15" ht="30.75" hidden="1">
+    <row r="13" spans="1:15" ht="30.75">
       <c r="A13" s="16" t="s">
         <v>71</v>
       </c>
@@ -2291,7 +2290,7 @@
       </c>
       <c r="O13" s="13"/>
     </row>
-    <row r="14" spans="1:15" ht="17.25" hidden="1">
+    <row r="14" spans="1:15" ht="17.25">
       <c r="A14" s="20" t="s">
         <v>72</v>
       </c>
@@ -2332,7 +2331,7 @@
       </c>
       <c r="O14" s="13"/>
     </row>
-    <row r="15" spans="1:15" ht="30.75" hidden="1">
+    <row r="15" spans="1:15" ht="30.75">
       <c r="A15" s="38" t="s">
         <v>76</v>
       </c>
@@ -2371,7 +2370,7 @@
       </c>
       <c r="O15" s="49"/>
     </row>
-    <row r="16" spans="1:15" ht="30.75" hidden="1">
+    <row r="16" spans="1:15" ht="30.75">
       <c r="A16" s="38" t="s">
         <v>79</v>
       </c>
@@ -2412,7 +2411,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="47.1" hidden="1" customHeight="1">
+    <row r="17" spans="1:16" ht="47.1" customHeight="1">
       <c r="A17" s="62" t="s">
         <v>82</v>
       </c>
@@ -2447,11 +2446,9 @@
       <c r="N17" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="O17" s="13" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="30.75" hidden="1">
+      <c r="O17" s="13"/>
+    </row>
+    <row r="18" spans="1:16" ht="30.75">
       <c r="A18" s="16" t="s">
         <v>87</v>
       </c>
@@ -2494,7 +2491,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="77.25" hidden="1">
+    <row r="19" spans="1:16" ht="77.25">
       <c r="A19" s="44" t="s">
         <v>94</v>
       </c>
@@ -2537,7 +2534,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="30.75" hidden="1">
+    <row r="20" spans="1:16" ht="30.75">
       <c r="A20" s="20" t="s">
         <v>101</v>
       </c>
@@ -2577,7 +2574,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="46.5" hidden="1">
+    <row r="21" spans="1:16" ht="46.5">
       <c r="A21" s="38" t="s">
         <v>104</v>
       </c>
@@ -2620,7 +2617,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="30.75" hidden="1">
+    <row r="22" spans="1:16" ht="30.75">
       <c r="A22" s="16" t="s">
         <v>109</v>
       </c>
@@ -2661,7 +2658,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="32.25" hidden="1">
+    <row r="23" spans="1:16" ht="32.25">
       <c r="A23" s="20" t="s">
         <v>115</v>
       </c>
@@ -2702,7 +2699,7 @@
       </c>
       <c r="O23" s="13"/>
     </row>
-    <row r="24" spans="1:16" ht="30.75" hidden="1">
+    <row r="24" spans="1:16" ht="30.75">
       <c r="A24" s="38" t="s">
         <v>120</v>
       </c>
@@ -2741,7 +2738,7 @@
       </c>
       <c r="O24" s="13"/>
     </row>
-    <row r="25" spans="1:16" hidden="1">
+    <row r="25" spans="1:16">
       <c r="A25" s="31" t="s">
         <v>124</v>
       </c>
@@ -2780,7 +2777,7 @@
       </c>
       <c r="O25" s="13"/>
     </row>
-    <row r="26" spans="1:16" ht="30.75" hidden="1">
+    <row r="26" spans="1:16" ht="30.75">
       <c r="A26" s="20" t="s">
         <v>127</v>
       </c>
@@ -2819,7 +2816,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="30.75" hidden="1">
+    <row r="27" spans="1:16" ht="30.75">
       <c r="A27" s="16" t="s">
         <v>132</v>
       </c>
@@ -2862,7 +2859,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="30.75" hidden="1">
+    <row r="28" spans="1:16" ht="30.75">
       <c r="A28" s="44" t="s">
         <v>139</v>
       </c>
@@ -2904,7 +2901,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="16.5" hidden="1">
+    <row r="29" spans="1:16" ht="16.5">
       <c r="A29" s="20" t="s">
         <v>143</v>
       </c>
@@ -2945,7 +2942,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="30.75" hidden="1">
+    <row r="30" spans="1:16" ht="30.75">
       <c r="A30" s="38" t="s">
         <v>146</v>
       </c>
@@ -2984,7 +2981,7 @@
       </c>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:16" ht="30.75" hidden="1">
+    <row r="31" spans="1:16" ht="30.75">
       <c r="A31" s="30" t="s">
         <v>151</v>
       </c>
@@ -3026,7 +3023,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="16.5" hidden="1">
+    <row r="32" spans="1:16" ht="16.5">
       <c r="A32" s="31" t="s">
         <v>155</v>
       </c>
@@ -3067,7 +3064,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:16" hidden="1">
+    <row r="33" spans="1:16">
       <c r="A33" s="31" t="s">
         <v>158</v>
       </c>
@@ -3106,7 +3103,7 @@
       </c>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:16" ht="30.75" hidden="1">
+    <row r="34" spans="1:16" ht="30.75">
       <c r="A34" s="37" t="s">
         <v>160</v>
       </c>
@@ -3145,7 +3142,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="32.25" hidden="1">
+    <row r="35" spans="1:16" ht="32.25">
       <c r="A35" s="31" t="s">
         <v>161</v>
       </c>
@@ -3186,7 +3183,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="32.25" hidden="1">
+    <row r="36" spans="1:16" ht="32.25">
       <c r="A36" s="57" t="s">
         <v>164</v>
       </c>
@@ -3227,7 +3224,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="30.75" hidden="1">
+    <row r="37" spans="1:16" ht="30.75">
       <c r="A37" s="31" t="s">
         <v>166</v>
       </c>
@@ -3268,7 +3265,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="16.5" hidden="1">
+    <row r="38" spans="1:16" ht="16.5">
       <c r="A38" s="56" t="s">
         <v>168</v>
       </c>
@@ -3307,7 +3304,7 @@
       </c>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:16" ht="16.5" hidden="1">
+    <row r="39" spans="1:16" ht="16.5">
       <c r="A39" s="20" t="s">
         <v>170</v>
       </c>
@@ -3346,7 +3343,7 @@
       </c>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:16" ht="30.75" hidden="1">
+    <row r="40" spans="1:16" ht="30.75">
       <c r="A40" s="56" t="s">
         <v>173</v>
       </c>
@@ -3385,7 +3382,7 @@
       </c>
       <c r="O40" s="13"/>
     </row>
-    <row r="41" spans="1:16" ht="16.5" hidden="1">
+    <row r="41" spans="1:16" ht="16.5">
       <c r="A41" s="31" t="s">
         <v>175</v>
       </c>
@@ -3424,7 +3421,7 @@
       </c>
       <c r="O41" s="13"/>
     </row>
-    <row r="42" spans="1:16" ht="15.75" hidden="1" customHeight="1">
+    <row r="42" spans="1:16" ht="15.75" customHeight="1">
       <c r="A42" s="16" t="s">
         <v>178</v>
       </c>
@@ -3461,7 +3458,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="15.75" hidden="1" customHeight="1">
+    <row r="43" spans="1:16" ht="15.75" customHeight="1">
       <c r="A43" s="20" t="s">
         <v>180</v>
       </c>
@@ -3500,7 +3497,7 @@
       </c>
       <c r="O43" s="13"/>
     </row>
-    <row r="44" spans="1:16" ht="15.75" hidden="1" customHeight="1">
+    <row r="44" spans="1:16" ht="15.75" customHeight="1">
       <c r="A44" s="20" t="s">
         <v>186</v>
       </c>
@@ -3528,7 +3525,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="15.75" hidden="1" customHeight="1">
+    <row r="45" spans="1:16" ht="15.75" customHeight="1">
       <c r="A45" s="20" t="s">
         <v>188</v>
       </c>
@@ -3563,11 +3560,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:N45" xr:uid="{8B6F68A8-D7AA-5040-AAF5-F610612294E8}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="PROI-511_x000a_PROI-712"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N45">
       <sortCondition ref="I1:I41"/>
     </sortState>

--- a/public/matriz_backlog.xlsx
+++ b/public/matriz_backlog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miguelangelpacheco/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="160" documentId="13_ncr:1_{E37656EC-6E73-A645-AFB7-232402410A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0D101C2-CCCC-4F38-9C6C-533323EF13BA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B5C3DE1-D478-460C-A599-15B2720E081B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{F5EBCA54-F250-EF45-B6B3-60EFDB3A97A7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Proyectos - Nego - Regu" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proyectos - Nego - Regu'!$A$1:$N$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proyectos - Nego - Regu'!$A$1:$P$45</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -796,6 +796,9 @@
     <t>16/10 - 22/10</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
     <t>PROI-739
 PROI-938</t>
   </si>
@@ -810,9 +813,6 @@
   </si>
   <si>
     <t>2/11 - 5/11</t>
-  </si>
-  <si>
-    <t>Miguel P.</t>
   </si>
   <si>
     <t>Carlos Vilca</t>
@@ -1738,7 +1738,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B6F68A8-D7AA-5040-AAF5-F610612294E8}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P45"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
@@ -1802,7 +1801,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="61.5" hidden="1">
+    <row r="2" spans="1:15" ht="61.5">
       <c r="A2" s="24" t="s">
         <v>15</v>
       </c>
@@ -1878,7 +1877,7 @@
       </c>
       <c r="O3" s="29"/>
     </row>
-    <row r="4" spans="1:15" ht="30.75" hidden="1">
+    <row r="4" spans="1:15" ht="30.75">
       <c r="A4" s="16" t="s">
         <v>31</v>
       </c>
@@ -1921,7 +1920,7 @@
       </c>
       <c r="O4" s="29"/>
     </row>
-    <row r="5" spans="1:15" ht="30.75" hidden="1">
+    <row r="5" spans="1:15" ht="30.75">
       <c r="A5" s="16" t="s">
         <v>37</v>
       </c>
@@ -1966,7 +1965,7 @@
       </c>
       <c r="O5" s="29"/>
     </row>
-    <row r="6" spans="1:15" ht="30.75" hidden="1">
+    <row r="6" spans="1:15" ht="30.75">
       <c r="A6" s="16" t="s">
         <v>43</v>
       </c>
@@ -2009,7 +2008,7 @@
       </c>
       <c r="O6" s="29"/>
     </row>
-    <row r="7" spans="1:15" hidden="1">
+    <row r="7" spans="1:15">
       <c r="A7" s="16" t="s">
         <v>46</v>
       </c>
@@ -2044,7 +2043,7 @@
       </c>
       <c r="O7" s="13"/>
     </row>
-    <row r="8" spans="1:15" ht="61.5" hidden="1">
+    <row r="8" spans="1:15" ht="61.5">
       <c r="A8" s="16" t="s">
         <v>49</v>
       </c>
@@ -2085,7 +2084,7 @@
       </c>
       <c r="O8" s="13"/>
     </row>
-    <row r="9" spans="1:15" ht="30.75" hidden="1">
+    <row r="9" spans="1:15" ht="30.75">
       <c r="A9" s="40" t="s">
         <v>55</v>
       </c>
@@ -2124,7 +2123,7 @@
       </c>
       <c r="O9" s="45"/>
     </row>
-    <row r="10" spans="1:15" ht="30.75" hidden="1">
+    <row r="10" spans="1:15" ht="30.75">
       <c r="A10" s="40" t="s">
         <v>58</v>
       </c>
@@ -2321,7 +2320,7 @@
       </c>
       <c r="O14" s="13"/>
     </row>
-    <row r="15" spans="1:15" ht="77.25" hidden="1">
+    <row r="15" spans="1:15" ht="77.25">
       <c r="A15" s="46" t="s">
         <v>74</v>
       </c>
@@ -2362,7 +2361,7 @@
       </c>
       <c r="O15" s="51"/>
     </row>
-    <row r="16" spans="1:15" ht="46.5" hidden="1">
+    <row r="16" spans="1:15" ht="46.5">
       <c r="A16" s="40" t="s">
         <v>80</v>
       </c>
@@ -2405,7 +2404,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="47.1" hidden="1" customHeight="1">
+    <row r="17" spans="1:16" ht="47.1" customHeight="1">
       <c r="A17" s="17" t="s">
         <v>86</v>
       </c>
@@ -2444,7 +2443,7 @@
       </c>
       <c r="O17" s="13"/>
     </row>
-    <row r="18" spans="1:16" ht="30.75" hidden="1">
+    <row r="18" spans="1:16" ht="30.75">
       <c r="A18" s="40" t="s">
         <v>91</v>
       </c>
@@ -2485,7 +2484,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="30.75" hidden="1">
+    <row r="19" spans="1:16" ht="30.75">
       <c r="A19" s="16" t="s">
         <v>97</v>
       </c>
@@ -2528,7 +2527,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="30.75" hidden="1">
+    <row r="20" spans="1:16" ht="30.75">
       <c r="A20" s="46" t="s">
         <v>105</v>
       </c>
@@ -2570,7 +2569,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="30.75" hidden="1">
+    <row r="21" spans="1:16" ht="30.75">
       <c r="A21" s="40" t="s">
         <v>108</v>
       </c>
@@ -2611,7 +2610,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="30.75" hidden="1">
+    <row r="22" spans="1:16" ht="30.75">
       <c r="A22" s="31" t="s">
         <v>114</v>
       </c>
@@ -2652,7 +2651,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:16" hidden="1">
+    <row r="23" spans="1:16">
       <c r="A23" s="32" t="s">
         <v>118</v>
       </c>
@@ -2730,7 +2729,7 @@
       </c>
       <c r="O24" s="13"/>
     </row>
-    <row r="25" spans="1:16" ht="30.75" hidden="1">
+    <row r="25" spans="1:16" ht="30.75">
       <c r="A25" s="39" t="s">
         <v>124</v>
       </c>
@@ -2767,7 +2766,7 @@
       </c>
       <c r="O25" s="13"/>
     </row>
-    <row r="26" spans="1:16" hidden="1">
+    <row r="26" spans="1:16">
       <c r="A26" s="32" t="s">
         <v>126</v>
       </c>
@@ -2849,7 +2848,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="28" spans="1:16" hidden="1">
+    <row r="28" spans="1:16">
       <c r="A28" s="64" t="s">
         <v>134</v>
       </c>
@@ -2891,7 +2890,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="30.75" hidden="1">
+    <row r="29" spans="1:16" ht="30.75">
       <c r="A29" s="32" t="s">
         <v>137</v>
       </c>
@@ -2932,7 +2931,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="32.25" hidden="1">
+    <row r="30" spans="1:16" ht="32.25">
       <c r="A30" s="21" t="s">
         <v>140</v>
       </c>
@@ -2973,7 +2972,7 @@
       </c>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:16" ht="16.5" hidden="1">
+    <row r="31" spans="1:16" ht="16.5">
       <c r="A31" s="21" t="s">
         <v>142</v>
       </c>
@@ -3017,7 +3016,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="32.25" hidden="1">
+    <row r="32" spans="1:16" ht="32.25">
       <c r="A32" s="21" t="s">
         <v>147</v>
       </c>
@@ -3060,7 +3059,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="17.25" hidden="1">
+    <row r="33" spans="1:16" ht="17.25">
       <c r="A33" s="21" t="s">
         <v>151</v>
       </c>
@@ -3142,7 +3141,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="32.25" hidden="1">
+    <row r="35" spans="1:16" ht="32.25">
       <c r="A35" s="58" t="s">
         <v>157</v>
       </c>
@@ -3183,7 +3182,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="32.25" hidden="1">
+    <row r="36" spans="1:16" ht="32.25">
       <c r="A36" s="21" t="s">
         <v>159</v>
       </c>
@@ -3224,7 +3223,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="30.75" hidden="1">
+    <row r="37" spans="1:16" ht="30.75">
       <c r="A37" s="58" t="s">
         <v>162</v>
       </c>
@@ -3265,7 +3264,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="16.5" hidden="1">
+    <row r="38" spans="1:16" ht="16.5">
       <c r="A38" s="32" t="s">
         <v>164</v>
       </c>
@@ -3304,7 +3303,7 @@
       </c>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:16" ht="16.5" hidden="1">
+    <row r="39" spans="1:16" ht="16.5">
       <c r="A39" s="32" t="s">
         <v>169</v>
       </c>
@@ -3343,7 +3342,7 @@
       </c>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:16" ht="30.75" hidden="1">
+    <row r="40" spans="1:16" ht="30.75">
       <c r="A40" s="21" t="s">
         <v>172</v>
       </c>
@@ -3376,13 +3375,13 @@
         <v>23</v>
       </c>
       <c r="N40" s="13" t="s">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="O40" s="13"/>
     </row>
     <row r="41" spans="1:16" ht="30.75">
       <c r="A41" s="21" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>173</v>
@@ -3403,7 +3402,7 @@
         <v>46331</v>
       </c>
       <c r="J41" s="19" t="s">
-        <v>128</v>
+        <v>35</v>
       </c>
       <c r="K41" s="19"/>
       <c r="L41" s="2" t="s">
@@ -3413,16 +3412,16 @@
         <v>23</v>
       </c>
       <c r="N41" s="13" t="s">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="O41" s="13"/>
     </row>
-    <row r="42" spans="1:16" ht="15.75" hidden="1" customHeight="1">
+    <row r="42" spans="1:16" ht="15.75" customHeight="1">
       <c r="A42" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>17</v>
@@ -3431,16 +3430,16 @@
         <v>57</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G42" s="35"/>
       <c r="H42" s="35"/>
       <c r="I42" s="35"/>
       <c r="J42" s="19" t="s">
-        <v>181</v>
+        <v>35</v>
       </c>
       <c r="K42" s="19" t="s">
         <v>182</v>
@@ -3458,7 +3457,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="15.75" hidden="1" customHeight="1">
+    <row r="43" spans="1:16" ht="15.75" customHeight="1">
       <c r="A43" s="21" t="s">
         <v>183</v>
       </c>
@@ -3495,7 +3494,7 @@
       </c>
       <c r="O43" s="13"/>
     </row>
-    <row r="44" spans="1:16" ht="15.75" hidden="1" customHeight="1">
+    <row r="44" spans="1:16" ht="15.75" customHeight="1">
       <c r="A44" s="21" t="s">
         <v>186</v>
       </c>
@@ -3523,7 +3522,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="15.75" hidden="1" customHeight="1">
+    <row r="45" spans="1:16" ht="15.75" customHeight="1">
       <c r="A45" s="21" t="s">
         <v>188</v>
       </c>
@@ -3557,14 +3556,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N45" xr:uid="{8B6F68A8-D7AA-5040-AAF5-F610612294E8}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="App"/>
-        <filter val="Web/App"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <hyperlinks>
     <hyperlink ref="A11" r:id="rId1" display="https://integratelperu.atlassian.net/browse/REQI-316" xr:uid="{0CC0A9FF-12B8-9B41-AE16-7A59C6261952}"/>
     <hyperlink ref="A12" r:id="rId2" display="https://integratelperu.atlassian.net/browse/REQI-323" xr:uid="{1DAF3C19-6C6E-8D40-B9EF-42AC8F043264}"/>

--- a/public/matriz_backlog.xlsx
+++ b/public/matriz_backlog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30611"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miguelangelpacheco/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B5C3DE1-D478-460C-A599-15B2720E081B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5154DC7C-3002-4FF7-A469-A25EDDB65EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{F5EBCA54-F250-EF45-B6B3-60EFDB3A97A7}"/>
   </bookViews>
@@ -2080,7 +2080,7 @@
         <v>23</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="O8" s="13"/>
     </row>
@@ -2158,7 +2158,7 @@
         <v>23</v>
       </c>
       <c r="N10" s="45" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="O10" s="45"/>
     </row>
@@ -3096,7 +3096,7 @@
         <v>64</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="O33" s="1"/>
     </row>
@@ -3556,6 +3556,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P45" xr:uid="{8B6F68A8-D7AA-5040-AAF5-F610612294E8}"/>
   <hyperlinks>
     <hyperlink ref="A11" r:id="rId1" display="https://integratelperu.atlassian.net/browse/REQI-316" xr:uid="{0CC0A9FF-12B8-9B41-AE16-7A59C6261952}"/>
     <hyperlink ref="A12" r:id="rId2" display="https://integratelperu.atlassian.net/browse/REQI-323" xr:uid="{1DAF3C19-6C6E-8D40-B9EF-42AC8F043264}"/>

--- a/public/matriz_backlog.xlsx
+++ b/public/matriz_backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miguelangelpacheco/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AAED0587-A0AE-422E-B7AA-62E3AA754C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{62862E1E-A68F-44E6-AC8A-4F11A34DE406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{F5EBCA54-F250-EF45-B6B3-60EFDB3A97A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="206">
   <si>
     <t>Proyecto</t>
   </si>
@@ -597,16 +597,16 @@
     <t>14/12 - 18/12</t>
   </si>
   <si>
+    <t>REQI-874</t>
+  </si>
+  <si>
+    <t>Activación de Contingencia para Continuidad de Ventas sin RENIEC Canal Presencial</t>
+  </si>
+  <si>
+    <t>9/10 - 16/10</t>
+  </si>
+  <si>
     <t>TBD</t>
-  </si>
-  <si>
-    <t>REQI-874</t>
-  </si>
-  <si>
-    <t>Activación de Contingencia para Continuidad de Ventas sin RENIEC Canal Presencial</t>
-  </si>
-  <si>
-    <t>9/10 - 16/10</t>
   </si>
   <si>
     <t>EAN Listo</t>
@@ -787,6 +787,9 @@
   </si>
   <si>
     <t>Functions</t>
+  </si>
+  <si>
+    <t>Producción</t>
   </si>
   <si>
     <t>REQI-823</t>
@@ -2539,8 +2542,8 @@
       </c>
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
-      <c r="I21" s="10" t="s">
-        <v>118</v>
+      <c r="I21" s="10">
+        <v>46413</v>
       </c>
       <c r="J21" s="10"/>
       <c r="K21" s="19" t="s">
@@ -2562,27 +2565,27 @@
     </row>
     <row r="22" spans="1:17" s="21" customFormat="1" ht="30.75">
       <c r="A22" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>119</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>120</v>
       </c>
       <c r="C22" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="40" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G22" s="20"/>
       <c r="H22" s="20"/>
       <c r="I22" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J22" s="20"/>
       <c r="K22" s="19" t="s">
@@ -2616,15 +2619,15 @@
         <v>125</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G23" s="20"/>
       <c r="H23" s="20"/>
       <c r="I23" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J23" s="20"/>
       <c r="K23" s="19" t="s">
@@ -2653,18 +2656,18 @@
         <v>29</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G24" s="20"/>
       <c r="H24" s="20"/>
       <c r="I24" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J24" s="20"/>
       <c r="K24" s="19" t="s">
@@ -2694,15 +2697,15 @@
       </c>
       <c r="D25" s="18"/>
       <c r="E25" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="20"/>
       <c r="I25" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J25" s="20"/>
       <c r="K25" s="19" t="s">
@@ -2734,10 +2737,10 @@
         <v>132</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G26" s="24"/>
       <c r="H26" s="24"/>
@@ -2773,18 +2776,18 @@
         <v>137</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G27" s="20"/>
       <c r="H27" s="20"/>
       <c r="I27" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J27" s="20"/>
       <c r="K27" s="42" t="s">
@@ -2815,18 +2818,18 @@
         <v>19</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G28" s="20"/>
       <c r="H28" s="20"/>
       <c r="I28" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J28" s="20"/>
       <c r="K28" s="19" t="s">
@@ -2858,18 +2861,18 @@
         <v>19</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G29" s="20"/>
       <c r="H29" s="20"/>
       <c r="I29" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J29" s="20"/>
       <c r="K29" s="19" t="s">
@@ -2990,10 +2993,10 @@
         <v>67</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
@@ -3115,18 +3118,18 @@
         <v>19</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
       <c r="I35" s="14" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J35" s="14"/>
       <c r="K35" s="15" t="s">
@@ -3160,15 +3163,15 @@
         <v>166</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G36" s="14"/>
       <c r="H36" s="14"/>
       <c r="I36" s="14" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J36" s="14"/>
       <c r="K36" s="15" t="s">
@@ -3199,18 +3202,18 @@
         <v>19</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G37" s="18"/>
       <c r="H37" s="18"/>
       <c r="I37" s="18" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J37" s="18"/>
       <c r="K37" s="19" t="s">
@@ -3266,28 +3269,28 @@
         <v>69</v>
       </c>
       <c r="O38" s="13" t="s">
-        <v>4</v>
+        <v>174</v>
       </c>
       <c r="P38" s="13"/>
     </row>
     <row r="39" spans="1:17" s="21" customFormat="1" ht="16.5">
       <c r="A39" s="42" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F39" s="40" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G39" s="20"/>
       <c r="H39" s="20"/>
@@ -3312,25 +3315,25 @@
     </row>
     <row r="40" spans="1:17" s="21" customFormat="1" ht="30.75">
       <c r="A40" s="46" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="18"/>
       <c r="E40" s="18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G40" s="24"/>
       <c r="H40" s="24"/>
       <c r="I40" s="24">
-        <v>46324</v>
+        <v>46338</v>
       </c>
       <c r="J40" s="24"/>
       <c r="K40" s="19" t="s">
@@ -3344,26 +3347,26 @@
         <v>25</v>
       </c>
       <c r="O40" s="20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P40" s="20"/>
     </row>
     <row r="41" spans="1:17" s="21" customFormat="1" ht="30.75">
       <c r="A41" s="46" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C41" s="18" t="s">
         <v>29</v>
       </c>
       <c r="D41" s="18"/>
       <c r="E41" s="18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F41" s="18" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G41" s="24"/>
       <c r="H41" s="24"/>
@@ -3382,16 +3385,16 @@
         <v>25</v>
       </c>
       <c r="O41" s="20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P41" s="20"/>
     </row>
     <row r="42" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A42" s="46" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>19</v>
@@ -3403,7 +3406,7 @@
         <v>63</v>
       </c>
       <c r="F42" s="18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G42" s="24"/>
       <c r="H42" s="24"/>
@@ -3413,7 +3416,7 @@
         <v>37</v>
       </c>
       <c r="L42" s="19" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M42" s="18" t="s">
         <v>44</v>
@@ -3430,7 +3433,7 @@
     </row>
     <row r="43" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A43" s="46" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B43" s="18" t="s">
         <v>130</v>
@@ -3440,10 +3443,10 @@
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F43" s="18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G43" s="24"/>
       <c r="H43" s="24"/>
@@ -3468,7 +3471,7 @@
     </row>
     <row r="44" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A44" s="46" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B44" s="18"/>
       <c r="C44" s="18" t="s">
@@ -3492,15 +3495,15 @@
       <c r="O44" s="20"/>
       <c r="P44" s="20"/>
       <c r="Q44" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A45" s="46" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C45" s="18" t="s">
         <v>19</v>
@@ -3531,7 +3534,7 @@
     </row>
     <row r="46" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A46" s="46" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B46" s="18"/>
       <c r="C46" s="18"/>
@@ -3547,15 +3550,15 @@
       <c r="M46" s="18"/>
       <c r="O46" s="20"/>
       <c r="P46" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A47" s="46" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C47" s="18"/>
       <c r="D47" s="18"/>
@@ -3574,7 +3577,7 @@
     </row>
     <row r="48" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A48" s="46" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B48" s="18"/>
       <c r="C48" s="18" t="s">
@@ -3600,22 +3603,22 @@
     </row>
     <row r="49" spans="1:15" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A49" s="25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O49" s="25"/>
     </row>
     <row r="50" spans="1:15" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A50" s="25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O50" s="25"/>
     </row>
     <row r="51" spans="1:15" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A51" s="25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C51" s="18" t="s">
         <v>19</v>
@@ -3627,10 +3630,10 @@
     </row>
     <row r="52" spans="1:15" ht="15.75" customHeight="1">
       <c r="A52" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B52" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C52" t="s">
         <v>19</v>

--- a/public/matriz_backlog.xlsx
+++ b/public/matriz_backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miguelangelpacheco/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62862E1E-A68F-44E6-AC8A-4F11A34DE406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{01119B08-5E1A-490C-8A79-59D2A15C27E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{F5EBCA54-F250-EF45-B6B3-60EFDB3A97A7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Proyectos - Nego - Regu" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proyectos - Nego - Regu'!$A$1:$Q$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proyectos - Nego - Regu'!$A$1:$Q$42</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="198">
   <si>
     <t>Proyecto</t>
   </si>
@@ -630,24 +630,6 @@
     <t>TV App</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">PROI-255
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow (Cuerpo)"/>
-      </rPr>
-      <t>PROI-699</t>
-    </r>
-  </si>
-  <si>
-    <t>Actualización de Condiciones de Uso (CDU)- Adecuaciones en herramientas - Parte 2</t>
-  </si>
-  <si>
     <t>PROI-852</t>
   </si>
   <si>
@@ -669,15 +651,15 @@
     <t>Web/App</t>
   </si>
   <si>
-    <t>EAN listo</t>
-  </si>
-  <si>
     <t>REQI-572</t>
   </si>
   <si>
     <t>Visualización en Dito opción repetidor Comodato y Alquiler</t>
   </si>
   <si>
+    <t>Idea</t>
+  </si>
+  <si>
     <t>Revisar con Joel</t>
   </si>
   <si>
@@ -687,30 +669,6 @@
     <t>Adecuaciones en la validación biométrica RENIEC/MIGRACIONES y venta a Clientes Extranjeros</t>
   </si>
   <si>
-    <t>Listo para estimar</t>
-  </si>
-  <si>
-    <t>REQI-846</t>
-  </si>
-  <si>
-    <t>Tren Apollo | Atención de Mejoras // Gaps // Incidencias // Configuraciones de aplicaciones Apollo - Setiembre</t>
-  </si>
-  <si>
-    <t>REQI-858</t>
-  </si>
-  <si>
-    <t>Tren Apollo | Upgrade de Framework a Genesis 3.3 - Setiembre</t>
-  </si>
-  <si>
-    <t>Backend</t>
-  </si>
-  <si>
-    <t>New</t>
-  </si>
-  <si>
-    <t>Crear reqi octubre</t>
-  </si>
-  <si>
     <t>REQI-152</t>
   </si>
   <si>
@@ -745,6 +703,9 @@
   </si>
   <si>
     <t>Monitoreo Diario-Flujo de subsanación cliente extranjero B2C</t>
+  </si>
+  <si>
+    <t>Aprobación control</t>
   </si>
   <si>
     <t>REQI-816</t>
@@ -780,6 +741,9 @@
     <t>Migración function runtime - java 21 - DITO</t>
   </si>
   <si>
+    <t>Backend</t>
+  </si>
+  <si>
     <t>07/09 - 25/09</t>
   </si>
   <si>
@@ -840,6 +804,9 @@
 PROI-942</t>
   </si>
   <si>
+    <t>Actualización de Condiciones de Uso (CDU)- Adecuaciones en herramientas - Parte 2</t>
+  </si>
+  <si>
     <t>1/12 - 17/12</t>
   </si>
   <si>
@@ -859,9 +826,6 @@
   </si>
   <si>
     <t>REQI-974</t>
-  </si>
-  <si>
-    <t>Idea</t>
   </si>
   <si>
     <t>PROI-724</t>
@@ -892,7 +856,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -996,6 +960,12 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF5A6B88"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1029,7 +999,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1146,12 +1116,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE1E7EF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1281,9 +1260,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1293,8 +1269,8 @@
     <xf numFmtId="16" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1658,7 +1634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B6F68A8-D7AA-5040-AAF5-F610612294E8}">
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.375" style="7" customWidth="1"/>
@@ -2685,103 +2661,107 @@
       </c>
       <c r="P24" s="20"/>
     </row>
-    <row r="25" spans="1:17" s="21" customFormat="1" ht="30.75">
-      <c r="A25" s="45" t="s">
+    <row r="25" spans="1:17" s="21" customFormat="1">
+      <c r="A25" s="42" t="s">
         <v>129</v>
       </c>
-      <c r="B25" s="44" t="s">
-        <v>130</v>
+      <c r="B25" s="17" t="s">
+        <v>74</v>
       </c>
       <c r="C25" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="18"/>
+      <c r="D25" s="20" t="s">
+        <v>130</v>
+      </c>
       <c r="E25" s="10" t="s">
         <v>121</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="J25" s="20"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24">
+        <v>46366</v>
+      </c>
+      <c r="J25" s="24"/>
       <c r="K25" s="19" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
       <c r="L25" s="19"/>
       <c r="M25" s="20" t="s">
         <v>20</v>
       </c>
       <c r="N25" s="20" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O25" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="P25" s="20"/>
+      <c r="P25" s="20" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="26" spans="1:17" s="21" customFormat="1">
       <c r="A26" s="42" t="s">
-        <v>131</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>74</v>
+        <v>133</v>
+      </c>
+      <c r="B26" s="44" t="s">
+        <v>134</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24">
-        <v>46366</v>
-      </c>
-      <c r="J26" s="24"/>
-      <c r="K26" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="L26" s="19"/>
+        <v>121</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="J26" s="20"/>
+      <c r="K26" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" s="42"/>
       <c r="M26" s="20" t="s">
         <v>20</v>
       </c>
       <c r="N26" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="O26" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="P26" s="20" t="s">
-        <v>134</v>
+      <c r="O26" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="P26" s="48" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="21" customFormat="1">
       <c r="A27" s="42" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="D27" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="E27" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="F27" s="20" t="s">
+      <c r="E27" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F27" s="10" t="s">
         <v>121</v>
       </c>
       <c r="G27" s="20"/>
@@ -2790,29 +2770,32 @@
         <v>121</v>
       </c>
       <c r="J27" s="20"/>
-      <c r="K27" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="L27" s="42"/>
+      <c r="K27" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="L27" s="44"/>
       <c r="M27" s="20" t="s">
         <v>20</v>
       </c>
       <c r="N27" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="O27" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="P27" s="20" t="s">
+      <c r="O27" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" s="21" customFormat="1">
+      <c r="P27" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q27" s="21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" s="21" customFormat="1" ht="30.75">
       <c r="A28" s="42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B28" s="44" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>19</v>
@@ -2833,71 +2816,72 @@
       </c>
       <c r="J28" s="20"/>
       <c r="K28" s="19" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="L28" s="44"/>
-      <c r="M28" s="20" t="s">
-        <v>20</v>
+      <c r="M28" s="18" t="s">
+        <v>100</v>
       </c>
       <c r="N28" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="O28" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="21" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" s="21" customFormat="1" ht="30.75">
-      <c r="A29" s="42" t="s">
+      <c r="O28" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="P28" s="48" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" s="21" customFormat="1" ht="32.25">
+      <c r="A29" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="B29" s="44" t="s">
+      <c r="B29" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="J29" s="20"/>
-      <c r="K29" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="L29" s="44"/>
-      <c r="M29" s="18" t="s">
+      <c r="D29" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14">
+        <v>46408</v>
+      </c>
+      <c r="J29" s="14"/>
+      <c r="K29" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="L29" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="M29" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="N29" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="O29" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="P29" s="20" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" s="21" customFormat="1" ht="32.25">
-      <c r="A30" s="46" t="s">
+      <c r="N29" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="O29" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="P29" s="13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" s="21" customFormat="1" ht="17.25">
+      <c r="A30" s="45" t="s">
         <v>146</v>
+      </c>
+      <c r="B30" s="46" t="s">
+        <v>147</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>19</v>
@@ -2905,44 +2889,44 @@
       <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="E30" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>54</v>
       </c>
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
       <c r="I30" s="14">
-        <v>46296</v>
+        <v>46310</v>
       </c>
       <c r="J30" s="14"/>
       <c r="K30" s="15" t="s">
         <v>42</v>
       </c>
       <c r="L30" s="15" t="s">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="M30" s="13" t="s">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="N30" s="13" t="s">
         <v>69</v>
       </c>
       <c r="O30" s="13" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="P30" s="13"/>
     </row>
     <row r="31" spans="1:17" s="21" customFormat="1" ht="16.5">
-      <c r="A31" s="46" t="s">
-        <v>147</v>
+      <c r="A31" s="45" t="s">
+        <v>150</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -2955,105 +2939,98 @@
       </c>
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
-      <c r="I31" s="14">
-        <v>46236</v>
+      <c r="I31" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="J31" s="14"/>
       <c r="K31" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="L31" s="15" t="s">
-        <v>150</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="L31" s="15"/>
       <c r="M31" s="13" t="s">
-        <v>149</v>
+        <v>31</v>
       </c>
       <c r="N31" s="13" t="s">
         <v>69</v>
       </c>
       <c r="O31" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="P31" s="13"/>
-      <c r="Q31" s="21" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" s="21" customFormat="1" ht="32.25">
-      <c r="A32" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="P31" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" s="21" customFormat="1" ht="16.5">
+      <c r="A32" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="13" t="s">
         <v>153</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>19</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="E32" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="18" t="s">
         <v>121</v>
       </c>
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
-      <c r="I32" s="14">
-        <v>46353</v>
+      <c r="I32" s="14" t="s">
+        <v>121</v>
       </c>
       <c r="J32" s="14"/>
       <c r="K32" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="L32" s="15" t="s">
-        <v>154</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="L32" s="15"/>
       <c r="M32" s="13" t="s">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="N32" s="13" t="s">
         <v>69</v>
       </c>
       <c r="O32" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="P32" s="13" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" s="21" customFormat="1" ht="16.5">
+      <c r="A33" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="P32" s="13" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" s="21" customFormat="1" ht="17.25">
-      <c r="A33" s="46" t="s">
+      <c r="B33" s="13" t="s">
         <v>156</v>
-      </c>
-      <c r="B33" s="47" t="s">
-        <v>157</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>20</v>
+        <v>157</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
-      <c r="I33" s="14">
-        <v>46310</v>
+      <c r="I33" s="14" t="s">
+        <v>121</v>
       </c>
       <c r="J33" s="14"/>
       <c r="K33" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="L33" s="15" t="s">
-        <v>159</v>
-      </c>
+      <c r="L33" s="15"/>
       <c r="M33" s="13" t="s">
         <v>44</v>
       </c>
@@ -3061,119 +3038,119 @@
         <v>69</v>
       </c>
       <c r="O33" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="P33" s="13"/>
-    </row>
-    <row r="34" spans="1:17" s="21" customFormat="1" ht="16.5">
-      <c r="A34" s="46" t="s">
+        <v>145</v>
+      </c>
+      <c r="P33" s="13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" s="21" customFormat="1" ht="30.75">
+      <c r="A34" s="45" t="s">
+        <v>158</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="J34" s="18"/>
+      <c r="K34" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="L34" s="19"/>
+      <c r="M34" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="N34" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="O34" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="P34" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" s="21" customFormat="1" ht="16.5">
+      <c r="A35" s="42" t="s">
         <v>160</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B35" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D34" s="13" t="s">
+      <c r="C35" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E34" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J34" s="14"/>
-      <c r="K34" s="15" t="s">
+      <c r="E35" s="47" t="s">
+        <v>163</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24">
+        <v>46294</v>
+      </c>
+      <c r="J35" s="24"/>
+      <c r="K35" s="15" t="s">
         <v>23</v>
-      </c>
-      <c r="L34" s="15"/>
-      <c r="M34" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="N34" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="O34" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="P34" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" s="21" customFormat="1" ht="16.5">
-      <c r="A35" s="46" t="s">
-        <v>162</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="F35" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="J35" s="14"/>
-      <c r="K35" s="15" t="s">
-        <v>47</v>
       </c>
       <c r="L35" s="15"/>
       <c r="M35" s="13" t="s">
-        <v>44</v>
+        <v>165</v>
       </c>
       <c r="N35" s="13" t="s">
         <v>69</v>
       </c>
       <c r="O35" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="P35" s="13" t="s">
-        <v>155</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="P35" s="13"/>
     </row>
     <row r="36" spans="1:17" s="21" customFormat="1" ht="16.5">
-      <c r="A36" s="46" t="s">
-        <v>164</v>
+      <c r="A36" s="42" t="s">
+        <v>167</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C36" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D36" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="J36" s="14"/>
+      <c r="D36" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="F36" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="24">
+        <v>46331</v>
+      </c>
+      <c r="J36" s="20"/>
       <c r="K36" s="15" t="s">
         <v>42</v>
       </c>
@@ -3185,159 +3162,155 @@
         <v>69</v>
       </c>
       <c r="O36" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="P36" s="13" t="s">
-        <v>155</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="P36" s="13"/>
     </row>
     <row r="37" spans="1:17" s="21" customFormat="1" ht="30.75">
-      <c r="A37" s="46" t="s">
-        <v>167</v>
+      <c r="A37" s="45" t="s">
+        <v>171</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C37" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D37" s="18" t="s">
-        <v>121</v>
-      </c>
+      <c r="D37" s="18"/>
       <c r="E37" s="18" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="J37" s="18"/>
+        <v>174</v>
+      </c>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24">
+        <v>46338</v>
+      </c>
+      <c r="J37" s="24"/>
       <c r="K37" s="19" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L37" s="19"/>
       <c r="M37" s="18" t="s">
         <v>44</v>
       </c>
       <c r="N37" s="20" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="O37" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="P37" s="20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" s="21" customFormat="1" ht="16.5">
-      <c r="A38" s="42" t="s">
-        <v>169</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" s="48" t="s">
-        <v>171</v>
-      </c>
-      <c r="F38" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="P37" s="20"/>
+    </row>
+    <row r="38" spans="1:17" s="21" customFormat="1" ht="30.75">
+      <c r="A38" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="B38" s="18" t="s">
         <v>172</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>174</v>
       </c>
       <c r="G38" s="24"/>
       <c r="H38" s="24"/>
       <c r="I38" s="24">
-        <v>46294</v>
+        <v>46331</v>
       </c>
       <c r="J38" s="24"/>
-      <c r="K38" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="L38" s="15"/>
-      <c r="M38" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="N38" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="O38" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="P38" s="13"/>
-    </row>
-    <row r="39" spans="1:17" s="21" customFormat="1" ht="16.5">
-      <c r="A39" s="42" t="s">
+      <c r="K38" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L38" s="19"/>
+      <c r="M38" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="N38" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="O38" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="B39" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="C39" s="13" t="s">
+      <c r="P38" s="20"/>
+    </row>
+    <row r="39" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A39" s="45" t="s">
+        <v>177</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="C39" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D39" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="F39" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
+      <c r="D39" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
       <c r="I39" s="24">
-        <v>46331</v>
-      </c>
-      <c r="J39" s="20"/>
-      <c r="K39" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="L39" s="15"/>
-      <c r="M39" s="13" t="s">
+        <v>46338</v>
+      </c>
+      <c r="J39" s="24"/>
+      <c r="K39" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L39" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="M39" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="O39" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="P39" s="13"/>
-    </row>
-    <row r="40" spans="1:17" s="21" customFormat="1" ht="30.75">
-      <c r="A40" s="46" t="s">
-        <v>179</v>
+      <c r="N39" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="O39" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="P39" s="20" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A40" s="45" t="s">
+        <v>181</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="18"/>
       <c r="E40" s="18" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G40" s="24"/>
       <c r="H40" s="24"/>
       <c r="I40" s="24">
-        <v>46338</v>
+        <v>46422</v>
       </c>
       <c r="J40" s="24"/>
       <c r="K40" s="19" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L40" s="19"/>
       <c r="M40" s="18" t="s">
@@ -3347,136 +3320,102 @@
         <v>25</v>
       </c>
       <c r="O40" s="20" t="s">
-        <v>183</v>
+        <v>3</v>
       </c>
       <c r="P40" s="20"/>
     </row>
-    <row r="41" spans="1:17" s="21" customFormat="1" ht="30.75">
-      <c r="A41" s="46" t="s">
-        <v>184</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>180</v>
-      </c>
+    <row r="41" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A41" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="B41" s="18"/>
       <c r="C41" s="18" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D41" s="18"/>
-      <c r="E41" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="F41" s="18" t="s">
-        <v>182</v>
-      </c>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
       <c r="G41" s="24"/>
       <c r="H41" s="24"/>
-      <c r="I41" s="24">
-        <v>46331</v>
-      </c>
+      <c r="I41" s="24"/>
       <c r="J41" s="24"/>
       <c r="K41" s="19" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L41" s="19"/>
       <c r="M41" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="N41" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="O41" s="20" t="s">
-        <v>183</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N41" s="20"/>
+      <c r="O41" s="20"/>
       <c r="P41" s="20"/>
+      <c r="Q41" s="21" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="42" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A42" s="46" t="s">
-        <v>185</v>
+      <c r="A42" s="45" t="s">
+        <v>187</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D42" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="F42" s="18" t="s">
-        <v>187</v>
-      </c>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
       <c r="G42" s="24"/>
       <c r="H42" s="24"/>
       <c r="I42" s="24"/>
       <c r="J42" s="24"/>
       <c r="K42" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="L42" s="19" t="s">
-        <v>188</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="L42" s="19"/>
       <c r="M42" s="18" t="s">
         <v>44</v>
       </c>
       <c r="N42" s="20" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="P42" s="20" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A43" s="46" t="s">
+      <c r="A43" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="B43" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="C43" s="18" t="s">
-        <v>19</v>
-      </c>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
       <c r="D43" s="18"/>
-      <c r="E43" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="F43" s="18" t="s">
-        <v>191</v>
-      </c>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
       <c r="G43" s="24"/>
       <c r="H43" s="24"/>
-      <c r="I43" s="24">
-        <v>46422</v>
-      </c>
+      <c r="I43" s="24"/>
       <c r="J43" s="24"/>
-      <c r="K43" s="19" t="s">
-        <v>42</v>
-      </c>
+      <c r="K43" s="19"/>
       <c r="L43" s="19"/>
-      <c r="M43" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="N43" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="O43" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="20"/>
+      <c r="M43" s="18"/>
+      <c r="O43" s="20"/>
+      <c r="P43" s="20" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="44" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A44" s="46" t="s">
-        <v>192</v>
-      </c>
-      <c r="B44" s="18"/>
-      <c r="C44" s="18" t="s">
-        <v>19</v>
-      </c>
+      <c r="A44" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="C44" s="18"/>
       <c r="D44" s="18"/>
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
@@ -3484,27 +3423,17 @@
       <c r="H44" s="24"/>
       <c r="I44" s="24"/>
       <c r="J44" s="24"/>
-      <c r="K44" s="19" t="s">
-        <v>47</v>
-      </c>
+      <c r="K44" s="19"/>
       <c r="L44" s="19"/>
-      <c r="M44" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="N44" s="20"/>
+      <c r="M44" s="18"/>
       <c r="O44" s="20"/>
       <c r="P44" s="20"/>
-      <c r="Q44" s="21" t="s">
-        <v>193</v>
-      </c>
     </row>
     <row r="45" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A45" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="B45" s="18" t="s">
-        <v>195</v>
-      </c>
+      <c r="A45" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="B45" s="18"/>
       <c r="C45" s="18" t="s">
         <v>19</v>
       </c>
@@ -3516,25 +3445,18 @@
       <c r="I45" s="24"/>
       <c r="J45" s="24"/>
       <c r="K45" s="19" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="L45" s="19"/>
       <c r="M45" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="N45" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="O45" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="P45" s="20" t="s">
-        <v>122</v>
-      </c>
+      <c r="O45" s="20"/>
+      <c r="P45" s="20"/>
     </row>
     <row r="46" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A46" s="46" t="s">
-        <v>196</v>
+      <c r="A46" s="45" t="s">
+        <v>192</v>
       </c>
       <c r="B46" s="18"/>
       <c r="C46" s="18"/>
@@ -3549,17 +3471,13 @@
       <c r="L46" s="19"/>
       <c r="M46" s="18"/>
       <c r="O46" s="20"/>
-      <c r="P46" s="20" t="s">
-        <v>197</v>
-      </c>
+      <c r="P46" s="20"/>
     </row>
     <row r="47" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A47" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="B47" s="18" t="s">
-        <v>199</v>
-      </c>
+      <c r="A47" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="B47" s="18"/>
       <c r="C47" s="18"/>
       <c r="D47" s="18"/>
       <c r="E47" s="18"/>
@@ -3571,15 +3489,16 @@
       <c r="K47" s="19"/>
       <c r="L47" s="19"/>
       <c r="M47" s="18"/>
-      <c r="N47" s="20"/>
       <c r="O47" s="20"/>
       <c r="P47" s="20"/>
     </row>
     <row r="48" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A48" s="46" t="s">
-        <v>192</v>
-      </c>
-      <c r="B48" s="18"/>
+      <c r="A48" s="45" t="s">
+        <v>194</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>195</v>
+      </c>
       <c r="C48" s="18" t="s">
         <v>19</v>
       </c>
@@ -3591,89 +3510,63 @@
       <c r="I48" s="24"/>
       <c r="J48" s="24"/>
       <c r="K48" s="19" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="L48" s="19"/>
-      <c r="M48" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="N48" s="20"/>
+      <c r="M48" s="18"/>
       <c r="O48" s="20"/>
       <c r="P48" s="20"/>
     </row>
-    <row r="49" spans="1:15" s="21" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A49" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="O49" s="25"/>
-    </row>
-    <row r="50" spans="1:15" s="21" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A50" s="25" t="s">
-        <v>201</v>
-      </c>
-      <c r="O50" s="25"/>
-    </row>
-    <row r="51" spans="1:15" s="21" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A51" s="25" t="s">
-        <v>202</v>
-      </c>
-      <c r="B51" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="C51" s="18" t="s">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A49" s="45" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="K51" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="O51" s="25"/>
-    </row>
-    <row r="52" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A52" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="B52" t="s">
-        <v>205</v>
-      </c>
-      <c r="C52" t="s">
-        <v>19</v>
-      </c>
-      <c r="D52" s="18" t="s">
+      <c r="D49" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="F52" s="10" t="s">
+      <c r="E49" s="18"/>
+      <c r="F49" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="I52" s="10">
+      <c r="G49" s="24"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="24">
         <v>46324</v>
       </c>
-      <c r="J52" s="49"/>
-      <c r="K52" t="s">
+      <c r="J49" s="24"/>
+      <c r="K49" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="M52" s="18" t="s">
+      <c r="L49" s="19"/>
+      <c r="M49" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="N52" s="20" t="s">
+      <c r="N49" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="O52" s="7" t="s">
+      <c r="O49" s="20" t="s">
         <v>5</v>
       </c>
+      <c r="P49" s="20"/>
+      <c r="Q49" s="21"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q52" xr:uid="{8B6F68A8-D7AA-5040-AAF5-F610612294E8}"/>
+  <autoFilter ref="A1:Q49" xr:uid="{8B6F68A8-D7AA-5040-AAF5-F610612294E8}"/>
   <hyperlinks>
     <hyperlink ref="A11" r:id="rId1" display="https://integratelperu.atlassian.net/browse/REQI-316" xr:uid="{0CC0A9FF-12B8-9B41-AE16-7A59C6261952}"/>
     <hyperlink ref="A12" r:id="rId2" display="https://integratelperu.atlassian.net/browse/REQI-323" xr:uid="{1DAF3C19-6C6E-8D40-B9EF-42AC8F043264}"/>
-    <hyperlink ref="A32" r:id="rId3" display="https://integratelperu.atlassian.net/browse/REQI-152" xr:uid="{18827046-A945-6A41-B4C6-CDC5631297BC}"/>
-    <hyperlink ref="A34" r:id="rId4" display="https://integratelperu.atlassian.net/browse/REQI-322" xr:uid="{C4BDCE36-9A48-4244-BD52-36B6BC764EC3}"/>
-    <hyperlink ref="A35" r:id="rId5" display="https://integratelperu.atlassian.net/browse/REQI-809" xr:uid="{498C0518-9995-E647-AB68-6C028F4B4527}"/>
-    <hyperlink ref="A36" r:id="rId6" display="https://integratelperu.atlassian.net/browse/REQI-816" xr:uid="{119F0BF8-13FD-584D-AE92-116B303FE312}"/>
-    <hyperlink ref="A30" r:id="rId7" display="https://integratelperu.atlassian.net/browse/REQI-846" xr:uid="{6E269148-CAF4-F247-8010-B7206C5A45E1}"/>
-    <hyperlink ref="A31" r:id="rId8" display="https://integratelperu.atlassian.net/browse/REQI-858" xr:uid="{2E1C2721-8ADD-864C-B1BC-0C84684C62B9}"/>
-    <hyperlink ref="A37" r:id="rId9" display="https://integratelperu.atlassian.net/browse/PROI-255" xr:uid="{2B2EDADC-1A37-FA4D-8866-E027128C7575}"/>
-    <hyperlink ref="A33" r:id="rId10" display="https://integratelperu.atlassian.net/browse/REQI-152" xr:uid="{E8559D96-C5EB-E744-B568-210F209F8ADA}"/>
+    <hyperlink ref="A29" r:id="rId3" display="https://integratelperu.atlassian.net/browse/REQI-152" xr:uid="{18827046-A945-6A41-B4C6-CDC5631297BC}"/>
+    <hyperlink ref="A31" r:id="rId4" display="https://integratelperu.atlassian.net/browse/REQI-322" xr:uid="{C4BDCE36-9A48-4244-BD52-36B6BC764EC3}"/>
+    <hyperlink ref="A32" r:id="rId5" display="https://integratelperu.atlassian.net/browse/REQI-809" xr:uid="{498C0518-9995-E647-AB68-6C028F4B4527}"/>
+    <hyperlink ref="A33" r:id="rId6" display="https://integratelperu.atlassian.net/browse/REQI-816" xr:uid="{119F0BF8-13FD-584D-AE92-116B303FE312}"/>
+    <hyperlink ref="A34" r:id="rId7" display="https://integratelperu.atlassian.net/browse/PROI-255" xr:uid="{2B2EDADC-1A37-FA4D-8866-E027128C7575}"/>
+    <hyperlink ref="A30" r:id="rId8" display="https://integratelperu.atlassian.net/browse/REQI-152" xr:uid="{E8559D96-C5EB-E744-B568-210F209F8ADA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/matriz_backlog.xlsx
+++ b/public/matriz_backlog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miguelangelpacheco/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01119B08-5E1A-490C-8A79-59D2A15C27E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{956455F2-5413-4288-AE4C-8ADEDB2F2C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{F5EBCA54-F250-EF45-B6B3-60EFDB3A97A7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Proyectos - Nego - Regu" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proyectos - Nego - Regu'!$A$1:$Q$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Proyectos - Nego - Regu'!$A$1:$Q$49</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>

--- a/public/matriz_backlog.xlsx
+++ b/public/matriz_backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miguelangelpacheco/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{956455F2-5413-4288-AE4C-8ADEDB2F2C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3844445-8872-44D6-8ED6-3ED0599A61D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{F5EBCA54-F250-EF45-B6B3-60EFDB3A97A7}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="196">
   <si>
     <t>Proyecto</t>
   </si>
@@ -567,9 +567,6 @@
     <t>Adecuaciones en la validación biométrica RENIEC/MIGRACIONES y venta a Clientes Extranjeros en otros canales</t>
   </si>
   <si>
-    <t>Cancelar en jira</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">PROI-122
 </t>
@@ -658,9 +655,6 @@
   </si>
   <si>
     <t>Idea</t>
-  </si>
-  <si>
-    <t>Revisar con Joel</t>
   </si>
   <si>
     <t>PROI-858</t>
@@ -2328,7 +2322,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="21" customFormat="1" ht="47.1" customHeight="1">
+    <row r="17" spans="1:16" s="21" customFormat="1" ht="47.1" customHeight="1">
       <c r="A17" s="30" t="s">
         <v>91</v>
       </c>
@@ -2368,7 +2362,7 @@
       </c>
       <c r="P17" s="20"/>
     </row>
-    <row r="18" spans="1:17" s="21" customFormat="1" ht="30.75">
+    <row r="18" spans="1:16" s="21" customFormat="1" ht="30.75">
       <c r="A18" s="16" t="s">
         <v>96</v>
       </c>
@@ -2410,7 +2404,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="21" customFormat="1" ht="30.75">
+    <row r="19" spans="1:16" s="21" customFormat="1" ht="30.75">
       <c r="A19" s="16" t="s">
         <v>102</v>
       </c>
@@ -2454,7 +2448,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="21" customFormat="1" ht="30.75">
+    <row r="20" spans="1:16" s="21" customFormat="1" ht="30.75">
       <c r="A20" s="16" t="s">
         <v>110</v>
       </c>
@@ -2493,28 +2487,25 @@
         <v>50</v>
       </c>
       <c r="P20" s="20"/>
-      <c r="Q20" s="21" t="s">
+    </row>
+    <row r="21" spans="1:16" s="21" customFormat="1" ht="30.75">
+      <c r="A21" s="16" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" s="21" customFormat="1" ht="30.75">
-      <c r="A21" s="16" t="s">
+      <c r="B21" s="17" t="s">
         <v>113</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>114</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="F21" s="10" t="s">
         <v>116</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>117</v>
       </c>
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
@@ -2539,29 +2530,29 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="21" customFormat="1" ht="30.75">
+    <row r="22" spans="1:16" s="21" customFormat="1" ht="30.75">
       <c r="A22" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>118</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>119</v>
       </c>
       <c r="C22" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="40" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G22" s="20"/>
       <c r="H22" s="20"/>
       <c r="I22" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J22" s="20"/>
       <c r="K22" s="19" t="s">
@@ -2575,35 +2566,35 @@
         <v>32</v>
       </c>
       <c r="O22" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="P22" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" s="21" customFormat="1">
+      <c r="A23" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="P22" s="20" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" s="21" customFormat="1">
-      <c r="A23" s="42" t="s">
+      <c r="B23" s="43" t="s">
         <v>123</v>
-      </c>
-      <c r="B23" s="43" t="s">
-        <v>124</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D23" s="40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G23" s="20"/>
       <c r="H23" s="20"/>
       <c r="I23" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J23" s="20"/>
       <c r="K23" s="19" t="s">
@@ -2617,33 +2608,33 @@
         <v>32</v>
       </c>
       <c r="O23" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="P23" s="20"/>
+    </row>
+    <row r="24" spans="1:16" s="21" customFormat="1">
+      <c r="A24" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="P23" s="20"/>
-    </row>
-    <row r="24" spans="1:17" s="21" customFormat="1">
-      <c r="A24" s="42" t="s">
+      <c r="B24" s="44" t="s">
         <v>127</v>
-      </c>
-      <c r="B24" s="44" t="s">
-        <v>128</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>29</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G24" s="20"/>
       <c r="H24" s="20"/>
       <c r="I24" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J24" s="20"/>
       <c r="K24" s="19" t="s">
@@ -2657,13 +2648,13 @@
         <v>32</v>
       </c>
       <c r="O24" s="20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P24" s="20"/>
     </row>
-    <row r="25" spans="1:17" s="21" customFormat="1">
+    <row r="25" spans="1:16" s="21" customFormat="1">
       <c r="A25" s="42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B25" s="17" t="s">
         <v>74</v>
@@ -2672,13 +2663,13 @@
         <v>19</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G25" s="24"/>
       <c r="H25" s="24"/>
@@ -2687,7 +2678,7 @@
       </c>
       <c r="J25" s="24"/>
       <c r="K25" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L25" s="19"/>
       <c r="M25" s="20" t="s">
@@ -2697,35 +2688,35 @@
         <v>32</v>
       </c>
       <c r="O25" s="20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P25" s="20" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" s="21" customFormat="1">
+      <c r="A26" s="42" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" s="21" customFormat="1">
-      <c r="A26" s="42" t="s">
+      <c r="B26" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="B26" s="44" t="s">
+      <c r="C26" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="18" t="s">
-        <v>135</v>
-      </c>
       <c r="D26" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G26" s="20"/>
       <c r="H26" s="20"/>
       <c r="I26" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J26" s="20"/>
       <c r="K26" s="42" t="s">
@@ -2739,35 +2730,35 @@
         <v>32</v>
       </c>
       <c r="O26" s="48" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P26" s="48" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" s="21" customFormat="1">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" s="21" customFormat="1">
       <c r="A27" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" s="44" t="s">
         <v>136</v>
-      </c>
-      <c r="B27" s="44" t="s">
-        <v>137</v>
       </c>
       <c r="C27" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G27" s="20"/>
       <c r="H27" s="20"/>
       <c r="I27" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J27" s="20"/>
       <c r="K27" s="19" t="s">
@@ -2781,38 +2772,35 @@
         <v>32</v>
       </c>
       <c r="O27" t="s">
+        <v>137</v>
+      </c>
+      <c r="P27" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" s="21" customFormat="1" ht="30.75">
+      <c r="A28" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="P27" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q27" s="21" t="s">
+      <c r="B28" s="44" t="s">
         <v>139</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" s="21" customFormat="1" ht="30.75">
-      <c r="A28" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="B28" s="44" t="s">
-        <v>141</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G28" s="20"/>
       <c r="H28" s="20"/>
       <c r="I28" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J28" s="20"/>
       <c r="K28" s="19" t="s">
@@ -2826,18 +2814,18 @@
         <v>32</v>
       </c>
       <c r="O28" s="48" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P28" s="48" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" s="21" customFormat="1" ht="32.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" s="21" customFormat="1" ht="32.25">
       <c r="A29" s="45" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B29" s="46" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>19</v>
@@ -2846,10 +2834,10 @@
         <v>67</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
@@ -2861,7 +2849,7 @@
         <v>37</v>
       </c>
       <c r="L29" s="15" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>100</v>
@@ -2870,18 +2858,18 @@
         <v>69</v>
       </c>
       <c r="O29" s="13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="P29" s="13" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="21" customFormat="1" ht="17.25">
+    <row r="30" spans="1:16" s="21" customFormat="1" ht="17.25">
       <c r="A30" s="45" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B30" s="46" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>19</v>
@@ -2890,7 +2878,7 @@
         <v>20</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F30" s="14" t="s">
         <v>54</v>
@@ -2905,7 +2893,7 @@
         <v>42</v>
       </c>
       <c r="L30" s="15" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>44</v>
@@ -2918,12 +2906,12 @@
       </c>
       <c r="P30" s="13"/>
     </row>
-    <row r="31" spans="1:17" s="21" customFormat="1" ht="16.5">
+    <row r="31" spans="1:16" s="21" customFormat="1" ht="16.5">
       <c r="A31" s="45" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>29</v>
@@ -2960,29 +2948,29 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="21" customFormat="1" ht="16.5">
+    <row r="32" spans="1:16" s="21" customFormat="1" ht="16.5">
       <c r="A32" s="45" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>19</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
       <c r="I32" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J32" s="14"/>
       <c r="K32" s="15" t="s">
@@ -2996,35 +2984,35 @@
         <v>69</v>
       </c>
       <c r="O32" s="13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P32" s="13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="21" customFormat="1" ht="16.5">
       <c r="A33" s="45" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
       <c r="I33" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J33" s="14"/>
       <c r="K33" s="15" t="s">
@@ -3038,35 +3026,35 @@
         <v>69</v>
       </c>
       <c r="O33" s="13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="P33" s="13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="21" customFormat="1" ht="30.75">
       <c r="A34" s="45" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C34" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F34" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G34" s="18"/>
       <c r="H34" s="18"/>
       <c r="I34" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J34" s="18"/>
       <c r="K34" s="19" t="s">
@@ -3088,22 +3076,22 @@
     </row>
     <row r="35" spans="1:17" s="21" customFormat="1" ht="16.5">
       <c r="A35" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>160</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>162</v>
       </c>
       <c r="D35" s="20" t="s">
         <v>20</v>
       </c>
       <c r="E35" s="47" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G35" s="24"/>
       <c r="H35" s="24"/>
@@ -3116,34 +3104,34 @@
       </c>
       <c r="L35" s="15"/>
       <c r="M35" s="13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="N35" s="13" t="s">
         <v>69</v>
       </c>
       <c r="O35" s="13" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="P35" s="13"/>
     </row>
     <row r="36" spans="1:17" s="21" customFormat="1" ht="16.5">
       <c r="A36" s="42" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C36" s="13" t="s">
         <v>19</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F36" s="40" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G36" s="20"/>
       <c r="H36" s="20"/>
@@ -3162,26 +3150,26 @@
         <v>69</v>
       </c>
       <c r="O36" s="13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="P36" s="13"/>
     </row>
     <row r="37" spans="1:17" s="21" customFormat="1" ht="30.75">
       <c r="A37" s="45" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C37" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D37" s="18"/>
       <c r="E37" s="18" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G37" s="24"/>
       <c r="H37" s="24"/>
@@ -3200,26 +3188,26 @@
         <v>25</v>
       </c>
       <c r="O37" s="20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="P37" s="20"/>
     </row>
     <row r="38" spans="1:17" s="21" customFormat="1" ht="30.75">
       <c r="A38" s="45" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C38" s="18" t="s">
         <v>29</v>
       </c>
       <c r="D38" s="18"/>
       <c r="E38" s="18" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F38" s="18" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G38" s="24"/>
       <c r="H38" s="24"/>
@@ -3238,16 +3226,16 @@
         <v>25</v>
       </c>
       <c r="O38" s="20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="P38" s="20"/>
     </row>
     <row r="39" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A39" s="45" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C39" s="18" t="s">
         <v>19</v>
@@ -3259,7 +3247,7 @@
         <v>63</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G39" s="24"/>
       <c r="H39" s="24"/>
@@ -3271,7 +3259,7 @@
         <v>37</v>
       </c>
       <c r="L39" s="19" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M39" s="18" t="s">
         <v>44</v>
@@ -3283,25 +3271,25 @@
         <v>3</v>
       </c>
       <c r="P39" s="20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A40" s="45" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="18"/>
       <c r="E40" s="18" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G40" s="24"/>
       <c r="H40" s="24"/>
@@ -3326,7 +3314,7 @@
     </row>
     <row r="41" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A41" s="45" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="18" t="s">
@@ -3350,15 +3338,15 @@
       <c r="O41" s="20"/>
       <c r="P41" s="20"/>
       <c r="Q41" s="21" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A42" s="45" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>19</v>
@@ -3381,15 +3369,15 @@
         <v>25</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P42" s="20" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A43" s="45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B43" s="18"/>
       <c r="C43" s="18"/>
@@ -3405,15 +3393,15 @@
       <c r="M43" s="18"/>
       <c r="O43" s="20"/>
       <c r="P43" s="20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A44" s="45" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C44" s="18"/>
       <c r="D44" s="18"/>
@@ -3431,7 +3419,7 @@
     </row>
     <row r="45" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A45" s="45" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B45" s="18"/>
       <c r="C45" s="18" t="s">
@@ -3456,7 +3444,7 @@
     </row>
     <row r="46" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A46" s="45" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B46" s="18"/>
       <c r="C46" s="18"/>
@@ -3475,7 +3463,7 @@
     </row>
     <row r="47" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A47" s="45" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="18"/>
@@ -3494,10 +3482,10 @@
     </row>
     <row r="48" spans="1:17" s="21" customFormat="1" ht="15.75" customHeight="1">
       <c r="A48" s="45" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C48" s="18" t="s">
         <v>19</v>
@@ -3519,10 +3507,10 @@
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="45" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C49" s="18" t="s">
         <v>19</v>
